--- a/AT32 FOR LVGL/app/project/MDK_V5/AT32F403AVGT7_WorkBench_analysis.xlsx
+++ b/AT32 FOR LVGL/app/project/MDK_V5/AT32F403AVGT7_WorkBench_analysis.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="86">
   <si>
     <t>AT32F403AVGT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-3910e2.o</t>
+    <t>lto-llvm-5e356c.o</t>
   </si>
   <si>
     <t>startup_at32f403a_407.o</t>
@@ -35,25 +35,10 @@
     <t>libspace.o</t>
   </si>
   <si>
-    <t>btod.o</t>
-  </si>
-  <si>
-    <t>_printf_fp_dec.o</t>
-  </si>
-  <si>
-    <t>_printf_fp_hex.o</t>
-  </si>
-  <si>
     <t>flsbuf.o</t>
   </si>
   <si>
-    <t>__printf_flags_ss_wp.o</t>
-  </si>
-  <si>
-    <t>bigflt0.o</t>
-  </si>
-  <si>
-    <t>lc_ctype_c.o</t>
+    <t>__printf_flags_wp.o</t>
   </si>
   <si>
     <t>initio.o</t>
@@ -71,42 +56,27 @@
     <t>fopen.o</t>
   </si>
   <si>
-    <t>_printf_wctomb.o</t>
-  </si>
-  <si>
-    <t>_printf_hex_int_ll_ptr.o</t>
-  </si>
-  <si>
     <t>_printf_intcommon.o</t>
   </si>
   <si>
     <t>rt_memcpy_v6.o</t>
   </si>
   <si>
-    <t>lludiv10.o</t>
-  </si>
-  <si>
     <t>init_alloc.o</t>
   </si>
   <si>
-    <t>_printf_fp_infnan.o</t>
+    <t>_printf_hex_int.o</t>
   </si>
   <si>
     <t>strcmpv7em.o</t>
   </si>
   <si>
-    <t>_printf_longlong_dec.o</t>
-  </si>
-  <si>
     <t>_printf_dec.o</t>
   </si>
   <si>
     <t>llsdiv.o</t>
   </si>
   <si>
-    <t>_printf_oct_int_ll.o</t>
-  </si>
-  <si>
     <t>rt_memcpy_w.o</t>
   </si>
   <si>
@@ -116,7 +86,7 @@
     <t>__scatter.o</t>
   </si>
   <si>
-    <t>_printf_str.o</t>
+    <t>__dczerorl2.o</t>
   </si>
   <si>
     <t>defsig_rtmem_inner.o</t>
@@ -137,10 +107,7 @@
     <t>sys_stackheap_outer.o</t>
   </si>
   <si>
-    <t>lc_numeric_c.o</t>
-  </si>
-  <si>
-    <t>_c16rtomb.o</t>
+    <t>strcpy.o</t>
   </si>
   <si>
     <t>setvbuf.o</t>
@@ -152,75 +119,60 @@
     <t>ftell.o</t>
   </si>
   <si>
+    <t>strlen.o</t>
+  </si>
+  <si>
     <t>h1_extend.o</t>
   </si>
   <si>
     <t>defsig_rtred_inner.o</t>
   </si>
   <si>
+    <t>defsig_general.o</t>
+  </si>
+  <si>
+    <t>_printf_char_common.o</t>
+  </si>
+  <si>
+    <t>puts.o</t>
+  </si>
+  <si>
+    <t>init_aeabi.o</t>
+  </si>
+  <si>
+    <t>_printf_char_file.o</t>
+  </si>
+  <si>
+    <t>systick_wrapper_gnu.o</t>
+  </si>
+  <si>
+    <t>fputc.o</t>
+  </si>
+  <si>
+    <t>__scatter_zi.o</t>
+  </si>
+  <si>
+    <t>fz_wm.l</t>
+  </si>
+  <si>
+    <t>fpinit.o</t>
+  </si>
+  <si>
+    <t>noretval__2printf.o</t>
+  </si>
+  <si>
     <t>libinit2.o</t>
   </si>
   <si>
-    <t>defsig_general.o</t>
-  </si>
-  <si>
-    <t>m_wm.l</t>
-  </si>
-  <si>
-    <t>fpclassify.o</t>
-  </si>
-  <si>
-    <t>_printf_char_common.o</t>
-  </si>
-  <si>
-    <t>init_aeabi.o</t>
-  </si>
-  <si>
-    <t>_printf_wchar.o</t>
-  </si>
-  <si>
-    <t>_printf_char.o</t>
-  </si>
-  <si>
-    <t>_printf_charcount.o</t>
-  </si>
-  <si>
-    <t>_printf_truncate.o</t>
-  </si>
-  <si>
-    <t>_printf_char_file.o</t>
-  </si>
-  <si>
-    <t>fz_wm.l</t>
-  </si>
-  <si>
-    <t>systick_wrapper_gnu.o</t>
-  </si>
-  <si>
-    <t>fputc.o</t>
-  </si>
-  <si>
-    <t>__scatter_zi.o</t>
-  </si>
-  <si>
-    <t>fpinit.o</t>
-  </si>
-  <si>
-    <t>__scatter_copy.o</t>
-  </si>
-  <si>
-    <t>printf.o</t>
-  </si>
-  <si>
     <t>exit.o</t>
   </si>
   <si>
-    <t>rt_ctype_table.o</t>
-  </si>
-  <si>
     <t>aeabi_memset4.o</t>
   </si>
   <si>
+    <t>aeabi_memset.o</t>
+  </si>
+  <si>
     <t>sys_wrch.o</t>
   </si>
   <si>
@@ -248,15 +200,6 @@
     <t>defsig_exit.o</t>
   </si>
   <si>
-    <t>_printf_ll.o</t>
-  </si>
-  <si>
-    <t>_printf_l.o</t>
-  </si>
-  <si>
-    <t>rt_locale_intlibspace.o</t>
-  </si>
-  <si>
     <t>rt_errno_addr_intlibspace.o</t>
   </si>
   <si>
@@ -278,67 +221,10 @@
     <t>_printf_u.o</t>
   </si>
   <si>
-    <t>_printf_s.o</t>
-  </si>
-  <si>
-    <t>_printf_p.o</t>
-  </si>
-  <si>
-    <t>_printf_o.o</t>
-  </si>
-  <si>
-    <t>_printf_n.o</t>
-  </si>
-  <si>
-    <t>_printf_ls.o</t>
-  </si>
-  <si>
-    <t>_printf_llx.o</t>
-  </si>
-  <si>
-    <t>_printf_llu.o</t>
-  </si>
-  <si>
-    <t>_printf_llo.o</t>
-  </si>
-  <si>
-    <t>_printf_lli.o</t>
-  </si>
-  <si>
-    <t>_printf_lld.o</t>
-  </si>
-  <si>
-    <t>_printf_lc.o</t>
-  </si>
-  <si>
-    <t>_printf_i.o</t>
-  </si>
-  <si>
-    <t>_printf_g.o</t>
-  </si>
-  <si>
-    <t>_printf_f.o</t>
-  </si>
-  <si>
-    <t>_printf_e.o</t>
-  </si>
-  <si>
     <t>_printf_d.o</t>
   </si>
   <si>
-    <t>_printf_c.o</t>
-  </si>
-  <si>
-    <t>_printf_a.o</t>
-  </si>
-  <si>
     <t>__rtentry4.o</t>
-  </si>
-  <si>
-    <t>printf2.o</t>
-  </si>
-  <si>
-    <t>printf1.o</t>
   </si>
   <si>
     <t>hguard.o</t>
@@ -476,11 +362,11 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$116</c:f>
+              <c:f>ram_percent!$A$3:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="114"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-3910e2.o</c:v>
+                  <c:v>lto-llvm-5e356c.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f403a_407.o</c:v>
@@ -494,7 +380,7 @@
                 <c:pt idx="4">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="75">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -502,26 +388,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$116</c:f>
+              <c:f>ram_percent!$B$3:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="114"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>94.42632293701172</c:v>
+                  <c:v>98.70268249511719</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.794841289520264</c:v>
+                  <c:v>0.8832814693450928</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.889415979385376</c:v>
+                  <c:v>0.2070190906524658</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6522383689880371</c:v>
+                  <c:v>0.1518139988183975</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2371775805950165</c:v>
-                </c:pt>
-                <c:pt idx="113">
+                  <c:v>0.0552050918340683</c:v>
+                </c:pt>
+                <c:pt idx="75">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -589,349 +475,235 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$116</c:f>
+              <c:f>flash_percent!$A$3:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="114"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-3910e2.o</c:v>
+                  <c:v>lto-llvm-5e356c.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>c_w.l</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>btod.o</c:v>
+                  <c:v>flsbuf.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>_printf_fp_dec.o</c:v>
+                  <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>_printf_fp_hex.o</c:v>
+                  <c:v>__printf_flags_wp.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>flsbuf.o</c:v>
+                  <c:v>initio.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>startup_at32f403a_407.o</c:v>
+                  <c:v>stdio.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>__printf_flags_ss_wp.o</c:v>
+                  <c:v>fseek.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>bigflt0.o</c:v>
+                  <c:v>lludivv7m.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>lc_ctype_c.o</c:v>
+                  <c:v>fopen.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>initio.o</c:v>
+                  <c:v>_printf_intcommon.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>stdio.o</c:v>
+                  <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>fseek.o</c:v>
+                  <c:v>init_alloc.o</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>lludivv7m.o</c:v>
+                  <c:v>_printf_hex_int.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>fopen.o</c:v>
+                  <c:v>strcmpv7em.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>_printf_wctomb.o</c:v>
+                  <c:v>_printf_dec.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>_printf_hex_int_ll_ptr.o</c:v>
+                  <c:v>llsdiv.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>_printf_intcommon.o</c:v>
+                  <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>rt_memcpy_v6.o</c:v>
+                  <c:v>h1_alloc.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>lludiv10.o</c:v>
+                  <c:v>__scatter.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>init_alloc.o</c:v>
+                  <c:v>__dczerorl2.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>_printf_fp_infnan.o</c:v>
+                  <c:v>defsig_rtmem_inner.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>strcmpv7em.o</c:v>
+                  <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>_printf_longlong_dec.o</c:v>
+                  <c:v>h1_free.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>_printf_dec.o</c:v>
+                  <c:v>_printf_pad.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>llsdiv.o</c:v>
+                  <c:v>fclose.o</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>_printf_oct_int_ll.o</c:v>
+                  <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>rt_memcpy_w.o</c:v>
+                  <c:v>strcpy.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>h1_alloc.o</c:v>
+                  <c:v>setvbuf.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>__scatter.o</c:v>
+                  <c:v>rt_memclr.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>_printf_str.o</c:v>
+                  <c:v>ftell.o</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>defsig_rtmem_inner.o</c:v>
+                  <c:v>strlen.o</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>rt_memclr_w.o</c:v>
+                  <c:v>h1_extend.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>h1_free.o</c:v>
+                  <c:v>defsig_rtred_inner.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>_printf_pad.o</c:v>
+                  <c:v>defsig_general.o</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>fclose.o</c:v>
+                  <c:v>_printf_char_common.o</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>sys_stackheap_outer.o</c:v>
+                  <c:v>puts.o</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>lc_numeric_c.o</c:v>
+                  <c:v>init_aeabi.o</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>_c16rtomb.o</c:v>
+                  <c:v>_printf_char_file.o</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>setvbuf.o</c:v>
+                  <c:v>systick_wrapper_gnu.o</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>rt_memclr.o</c:v>
+                  <c:v>fputc.o</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>ftell.o</c:v>
+                  <c:v>__scatter_zi.o</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>h1_extend.o</c:v>
+                  <c:v>fz_wm.l</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>defsig_rtred_inner.o</c:v>
+                  <c:v>fpinit.o</c:v>
                 </c:pt>
                 <c:pt idx="44">
+                  <c:v>noretval__2printf.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
                   <c:v>libinit2.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
-                  <c:v>defsig_general.o</c:v>
-                </c:pt>
                 <c:pt idx="46">
-                  <c:v>m_wm.l</c:v>
+                  <c:v>exit.o</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>fpclassify.o</c:v>
+                  <c:v>aeabi_memset4.o</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>_printf_char_common.o</c:v>
+                  <c:v>aeabi_memset.o</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>init_aeabi.o</c:v>
+                  <c:v>sys_wrch.o</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>_printf_wchar.o</c:v>
+                  <c:v>defsig_rtred_outer.o</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>_printf_char.o</c:v>
+                  <c:v>defsig_rtmem_outer.o</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>_printf_charcount.o</c:v>
+                  <c:v>__printf_wp.o</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>_printf_truncate.o</c:v>
+                  <c:v>sys_exit.o</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>_printf_char_file.o</c:v>
+                  <c:v>stdio_streams.o</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>fz_wm.l</c:v>
+                  <c:v>h1_init.o</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>systick_wrapper_gnu.o</c:v>
+                  <c:v>__rtentry2.o</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>fputc.o</c:v>
+                  <c:v>rtexit2.o</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>__scatter_zi.o</c:v>
+                  <c:v>defsig_exit.o</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>fpinit.o</c:v>
+                  <c:v>rt_errno_addr_intlibspace.o</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>__scatter_copy.o</c:v>
+                  <c:v>libspace.o</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>printf.o</c:v>
+                  <c:v>ferror.o</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>exit.o</c:v>
+                  <c:v>__main.o</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>rt_ctype_table.o</c:v>
+                  <c:v>libshutdown2.o</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>aeabi_memset4.o</c:v>
+                  <c:v>heapauxi.o</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>sys_wrch.o</c:v>
+                  <c:v>_printf_x.o</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>defsig_rtred_outer.o</c:v>
+                  <c:v>_printf_u.o</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>defsig_rtmem_outer.o</c:v>
+                  <c:v>_printf_d.o</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>__printf_wp.o</c:v>
+                  <c:v>__rtentry4.o</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>sys_exit.o</c:v>
+                  <c:v>hguard.o</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>stdio_streams.o</c:v>
+                  <c:v>_printf_percent_end.o</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>h1_init.o</c:v>
+                  <c:v>use_no_semi.o</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>__rtentry2.o</c:v>
+                  <c:v>rtexit.o</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>rtexit2.o</c:v>
+                  <c:v>libshutdown.o</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>defsig_exit.o</c:v>
+                  <c:v>libinit.o</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>_printf_ll.o</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>_printf_l.o</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>rt_locale_intlibspace.o</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>rt_errno_addr_intlibspace.o</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>libspace.o</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>ferror.o</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>__main.o</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>libshutdown2.o</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>heapauxi.o</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>_printf_x.o</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>_printf_u.o</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>_printf_s.o</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>_printf_p.o</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>_printf_o.o</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>_printf_n.o</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>_printf_ls.o</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>_printf_llx.o</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>_printf_llu.o</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>_printf_llo.o</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>_printf_lli.o</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>_printf_lld.o</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>_printf_lc.o</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>_printf_i.o</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>_printf_g.o</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>_printf_f.o</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>_printf_e.o</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>_printf_d.o</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>_printf_c.o</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>_printf_a.o</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>__rtentry4.o</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>printf2.o</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>printf1.o</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>hguard.o</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>_printf_percent_end.o</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>use_no_semi.o</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>rtexit.o</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>libshutdown.o</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>libinit.o</c:v>
-                </c:pt>
-                <c:pt idx="113">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -939,350 +711,236 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$116</c:f>
+              <c:f>flash_percent!$B$3:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="114"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>64.44553375244141</c:v>
+                  <c:v>98.01877593994141</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17.25422859191895</c:v>
+                  <c:v>0.9402714967727661</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.164174318313599</c:v>
+                  <c:v>0.09191054105758667</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.719375610351563</c:v>
+                  <c:v>0.08618996292352676</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.310778737068176</c:v>
+                  <c:v>0.06273561716079712</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.7877748012542725</c:v>
+                  <c:v>0.05949395895004273</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.7387431263923645</c:v>
+                  <c:v>0.05034103989601135</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6684644818305969</c:v>
+                  <c:v>0.04729006811976433</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.6145297288894653</c:v>
+                  <c:v>0.04576458409428597</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5164664387702942</c:v>
+                  <c:v>0.04576458409428597</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5099288821220398</c:v>
+                  <c:v>0.03394206613302231</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4314782917499542</c:v>
+                  <c:v>0.0263146348297596</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.405328094959259</c:v>
+                  <c:v>0.0263146348297596</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3922530114650726</c:v>
+                  <c:v>0.0244077779352665</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.3922530114650726</c:v>
+                  <c:v>0.02364503405988216</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3203399479389191</c:v>
+                  <c:v>0.02288229204714298</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3072648644447327</c:v>
+                  <c:v>0.02211954817175865</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.2909209728240967</c:v>
+                  <c:v>0.01906857639551163</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.2255454808473587</c:v>
+                  <c:v>0.01792446151375771</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.2255454808473587</c:v>
+                  <c:v>0.01792446151375771</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2255454808473587</c:v>
+                  <c:v>0.01716171950101852</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2092016041278839</c:v>
+                  <c:v>0.01525486074388027</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2026640474796295</c:v>
+                  <c:v>0.01487348973751068</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2026640474796295</c:v>
+                  <c:v>0.01487348973751068</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1961265057325363</c:v>
+                  <c:v>0.01487348973751068</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1895889490842819</c:v>
+                  <c:v>0.01449211779981852</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1830514073371887</c:v>
+                  <c:v>0.01411074679344893</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1634387522935867</c:v>
+                  <c:v>0.01372937485575676</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1536324322223663</c:v>
+                  <c:v>0.01334800384938717</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1536324322223663</c:v>
+                  <c:v>0.012966631911695</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1340197771787643</c:v>
+                  <c:v>0.01258525997400284</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1307509988546372</c:v>
+                  <c:v>0.01182251702994108</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.12748222053051</c:v>
+                  <c:v>0.009915660135447979</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.12748222053051</c:v>
+                  <c:v>0.009915660135447979</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.12748222053051</c:v>
+                  <c:v>0.009534288197755814</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.1242134496569634</c:v>
+                  <c:v>0.009152916260063648</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1209446787834168</c:v>
+                  <c:v>0.008390173316001892</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.1176759004592896</c:v>
+                  <c:v>0.008390173316001892</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.1176759004592896</c:v>
+                  <c:v>0.00686468742787838</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.114407129585743</c:v>
+                  <c:v>0.006101944483816624</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.1111383512616158</c:v>
+                  <c:v>0.005339201539754868</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.1078695729374886</c:v>
+                  <c:v>0.005339201539754868</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.08498814702033997</c:v>
+                  <c:v>0.00495783006772399</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.08498814702033997</c:v>
+                  <c:v>0.00495783006772399</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.08171937614679337</c:v>
+                  <c:v>0.004576458130031824</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.08171937614679337</c:v>
+                  <c:v>0.004195086658000946</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.07845059782266617</c:v>
+                  <c:v>0.00343234371393919</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.07845059782266617</c:v>
+                  <c:v>0.003050972241908312</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.07845059782266617</c:v>
+                  <c:v>0.003050972241908312</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.07191304862499237</c:v>
+                  <c:v>0.002669600769877434</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.07191304862499237</c:v>
+                  <c:v>0.002669600769877434</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.07191304862499237</c:v>
+                  <c:v>0.002669600769877434</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.06537549942731857</c:v>
+                  <c:v>0.002669600769877434</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.05883795022964478</c:v>
+                  <c:v>0.002288229065015912</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.05883795022964478</c:v>
+                  <c:v>0.002288229065015912</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.05556917563080788</c:v>
+                  <c:v>0.002288229065015912</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.05230040103197098</c:v>
+                  <c:v>0.002288229065015912</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.04576285183429718</c:v>
+                  <c:v>0.001906857592985034</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.04576285183429718</c:v>
+                  <c:v>0.001906857592985034</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.04249407351016998</c:v>
+                  <c:v>0.001525486120954156</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.04249407351016998</c:v>
+                  <c:v>0.001525486120954156</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.03922529891133308</c:v>
+                  <c:v>0.001525486120954156</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.02941897511482239</c:v>
+                  <c:v>0.001525486120954156</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.02615020051598549</c:v>
+                  <c:v>0.001144114532507956</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.02615020051598549</c:v>
+                  <c:v>0.001144114532507956</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.02288142591714859</c:v>
+                  <c:v>0.001144114532507956</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.02288142591714859</c:v>
+                  <c:v>0.001144114532507956</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.02288142591714859</c:v>
+                  <c:v>0.001144114532507956</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.02288142591714859</c:v>
+                  <c:v>0.001144114532507956</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.01961264945566654</c:v>
+                  <c:v>0.000762743060477078</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.01961264945566654</c:v>
+                  <c:v>0.000762743060477078</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.01961264945566654</c:v>
+                  <c:v>0.000381371530238539</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.01961264945566654</c:v>
+                  <c:v>0.000381371530238539</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.01634387485682964</c:v>
+                  <c:v>0.000381371530238539</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.01634387485682964</c:v>
+                  <c:v>0.000381371530238539</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.01634387485682964</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.01634387485682964</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.01307510025799274</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.01307510025799274</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.01307510025799274</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.01307510025799274</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0.01307510025799274</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.009806324727833271</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>0.006537550128996372</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>0.006537550128996372</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>0.006537550128996372</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.006537550128996372</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0.003268775064498186</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>0.003268775064498186</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>0.003268775064498186</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>0.003268775064498186</c:v>
-                </c:pt>
-                <c:pt idx="113">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1387,8 +1045,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H116" totalsRowCount="1">
-  <autoFilter ref="A2:H115"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H78" totalsRowCount="1">
+  <autoFilter ref="A2:H77"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1404,8 +1062,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H116" totalsRowCount="1">
-  <autoFilter ref="A2:H115"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H78" totalsRowCount="1">
+  <autoFilter ref="A2:H77"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1705,7 +1363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1718,28 +1376,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1747,25 +1405,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>94.42632293701172</v>
+        <v>98.70268249511719</v>
       </c>
       <c r="C3" s="1">
-        <v>38220</v>
+        <v>171641</v>
       </c>
       <c r="D3" s="1">
-        <v>39431</v>
+        <v>514033</v>
       </c>
       <c r="E3" s="1">
-        <v>39092</v>
+        <v>381842</v>
       </c>
       <c r="F3" s="1">
-        <v>320</v>
+        <v>131803</v>
       </c>
       <c r="G3" s="1">
-        <v>19</v>
+        <v>388</v>
       </c>
       <c r="H3" s="1">
-        <v>38201</v>
+        <v>171253</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1773,7 +1431,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>3.794841289520264</v>
+        <v>0.8832814693450928</v>
       </c>
       <c r="C4" s="1">
         <v>1536</v>
@@ -1799,19 +1457,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>0.889415979385376</v>
+        <v>0.2070190906524658</v>
       </c>
       <c r="C5" s="1">
         <v>360</v>
       </c>
       <c r="D5" s="1">
-        <v>10557</v>
+        <v>4931</v>
       </c>
       <c r="E5" s="1">
-        <v>9994</v>
+        <v>4862</v>
       </c>
       <c r="F5" s="1">
-        <v>551</v>
+        <v>57</v>
       </c>
       <c r="G5" s="1">
         <v>12</v>
@@ -1825,7 +1483,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.6522383689880371</v>
+        <v>0.1518139988183975</v>
       </c>
       <c r="C6" s="1">
         <v>264</v>
@@ -1851,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2371775805950165</v>
+        <v>0.0552050918340683</v>
       </c>
       <c r="C7" s="1">
         <v>96</v>
@@ -1872,35 +1530,35 @@
         <v>96</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
-      <c r="A116" t="s">
-        <v>115</v>
-      </c>
-      <c r="B116">
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C116">
+      <c r="C78">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D116">
+      <c r="D78">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E116">
+      <c r="E78">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F116">
+      <c r="F78">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G116">
+      <c r="G78">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H116">
+      <c r="H78">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1916,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1929,28 +1587,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1958,25 +1616,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>64.44553375244141</v>
+        <v>98.01877593994141</v>
       </c>
       <c r="C3" s="1">
-        <v>39431</v>
+        <v>514033</v>
       </c>
       <c r="D3" s="1">
-        <v>38220</v>
+        <v>171641</v>
       </c>
       <c r="E3" s="1">
-        <v>39092</v>
+        <v>381842</v>
       </c>
       <c r="F3" s="1">
-        <v>320</v>
+        <v>131803</v>
       </c>
       <c r="G3" s="1">
-        <v>19</v>
+        <v>388</v>
       </c>
       <c r="H3" s="1">
-        <v>38201</v>
+        <v>171253</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1984,19 +1642,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>17.25422859191895</v>
+        <v>0.9402714967727661</v>
       </c>
       <c r="C4" s="1">
-        <v>10557</v>
+        <v>4931</v>
       </c>
       <c r="D4" s="1">
         <v>360</v>
       </c>
       <c r="E4" s="1">
-        <v>9994</v>
+        <v>4862</v>
       </c>
       <c r="F4" s="1">
-        <v>551</v>
+        <v>57</v>
       </c>
       <c r="G4" s="1">
         <v>12</v>
@@ -2010,16 +1668,16 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>3.164174318313599</v>
+        <v>0.09191054105758667</v>
       </c>
       <c r="C5" s="1">
-        <v>1936</v>
+        <v>482</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>1936</v>
+        <v>482</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2033,48 +1691,48 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>1.719375610351563</v>
+        <v>0.08618996292352676</v>
       </c>
       <c r="C6" s="1">
-        <v>1052</v>
+        <v>452</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="E6" s="1">
-        <v>1052</v>
+        <v>64</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>1.310778737068176</v>
+        <v>0.06273561716079712</v>
       </c>
       <c r="C7" s="1">
-        <v>802</v>
+        <v>329</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>764</v>
+        <v>312</v>
       </c>
       <c r="F7" s="1">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -2085,19 +1743,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.7877748012542725</v>
+        <v>0.05949395895004273</v>
       </c>
       <c r="C8" s="1">
-        <v>482</v>
+        <v>312</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>482</v>
+        <v>312</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -2111,28 +1769,28 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>0.7387431263923645</v>
+        <v>0.05034103989601135</v>
       </c>
       <c r="C9" s="1">
-        <v>452</v>
+        <v>264</v>
       </c>
       <c r="D9" s="1">
-        <v>1536</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>64</v>
+        <v>264</v>
       </c>
       <c r="F9" s="1">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>1536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2140,19 +1798,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>0.6684644818305969</v>
+        <v>0.04729006811976433</v>
       </c>
       <c r="C10" s="1">
-        <v>409</v>
+        <v>248</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>392</v>
+        <v>248</v>
       </c>
       <c r="F10" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -2166,19 +1824,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>0.6145297288894653</v>
+        <v>0.04576458409428597</v>
       </c>
       <c r="C11" s="1">
-        <v>376</v>
+        <v>240</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="F11" s="1">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -2192,19 +1850,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>0.5164664387702942</v>
+        <v>0.04576458409428597</v>
       </c>
       <c r="C12" s="1">
-        <v>316</v>
+        <v>240</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>44</v>
+        <v>240</v>
       </c>
       <c r="F12" s="1">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -2218,16 +1876,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>0.5099288821220398</v>
+        <v>0.03394206613302231</v>
       </c>
       <c r="C13" s="1">
-        <v>312</v>
+        <v>178</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>312</v>
+        <v>178</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2244,16 +1902,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>0.4314782917499542</v>
+        <v>0.0263146348297596</v>
       </c>
       <c r="C14" s="1">
-        <v>264</v>
+        <v>138</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>264</v>
+        <v>138</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2270,16 +1928,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>0.405328094959259</v>
+        <v>0.0263146348297596</v>
       </c>
       <c r="C15" s="1">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2296,19 +1954,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>0.3922530114650726</v>
+        <v>0.0244077779352665</v>
       </c>
       <c r="C16" s="1">
-        <v>240</v>
+        <v>128</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>240</v>
+        <v>88</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -2322,16 +1980,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>0.3922530114650726</v>
+        <v>0.02364503405988216</v>
       </c>
       <c r="C17" s="1">
-        <v>240</v>
+        <v>124</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>240</v>
+        <v>124</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2348,19 +2006,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>0.3203399479389191</v>
+        <v>0.02288229204714298</v>
       </c>
       <c r="C18" s="1">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>188</v>
+        <v>120</v>
       </c>
       <c r="F18" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -2374,19 +2032,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3072648644447327</v>
+        <v>0.02211954817175865</v>
       </c>
       <c r="C19" s="1">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="F19" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -2400,16 +2058,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>0.2909209728240967</v>
+        <v>0.01906857639551163</v>
       </c>
       <c r="C20" s="1">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2426,16 +2084,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>0.2255454808473587</v>
+        <v>0.01792446151375771</v>
       </c>
       <c r="C21" s="1">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2452,16 +2110,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>0.2255454808473587</v>
+        <v>0.01792446151375771</v>
       </c>
       <c r="C22" s="1">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2478,16 +2136,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2255454808473587</v>
+        <v>0.01716171950101852</v>
       </c>
       <c r="C23" s="1">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2504,16 +2162,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2092016041278839</v>
+        <v>0.01525486074388027</v>
       </c>
       <c r="C24" s="1">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2530,16 +2188,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2026640474796295</v>
+        <v>0.01487348973751068</v>
       </c>
       <c r="C25" s="1">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2556,16 +2214,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2026640474796295</v>
+        <v>0.01487348973751068</v>
       </c>
       <c r="C26" s="1">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2582,16 +2240,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1961265057325363</v>
+        <v>0.01487348973751068</v>
       </c>
       <c r="C27" s="1">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2608,16 +2266,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1895889490842819</v>
+        <v>0.01449211779981852</v>
       </c>
       <c r="C28" s="1">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2634,16 +2292,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1830514073371887</v>
+        <v>0.01411074679344893</v>
       </c>
       <c r="C29" s="1">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2660,16 +2318,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1634387522935867</v>
+        <v>0.01372937485575676</v>
       </c>
       <c r="C30" s="1">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2686,16 +2344,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1536324322223663</v>
+        <v>0.01334800384938717</v>
       </c>
       <c r="C31" s="1">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2712,16 +2370,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1536324322223663</v>
+        <v>0.012966631911695</v>
       </c>
       <c r="C32" s="1">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2738,16 +2396,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1340197771787643</v>
+        <v>0.01258525997400284</v>
       </c>
       <c r="C33" s="1">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2764,16 +2422,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1307509988546372</v>
+        <v>0.01182251702994108</v>
       </c>
       <c r="C34" s="1">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2790,16 +2448,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="2">
-        <v>0.12748222053051</v>
+        <v>0.009915660135447979</v>
       </c>
       <c r="C35" s="1">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2816,16 +2474,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="2">
-        <v>0.12748222053051</v>
+        <v>0.009915660135447979</v>
       </c>
       <c r="C36" s="1">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2842,16 +2500,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>0.12748222053051</v>
+        <v>0.009534288197755814</v>
       </c>
       <c r="C37" s="1">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2868,16 +2526,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>0.1242134496569634</v>
+        <v>0.009152916260063648</v>
       </c>
       <c r="C38" s="1">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2894,16 +2552,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.1209446787834168</v>
+        <v>0.008390173316001892</v>
       </c>
       <c r="C39" s="1">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2920,10 +2578,10 @@
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.1176759004592896</v>
+        <v>0.008390173316001892</v>
       </c>
       <c r="C40" s="1">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
@@ -2932,7 +2590,7 @@
         <v>44</v>
       </c>
       <c r="F40" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
@@ -2946,16 +2604,16 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.1176759004592896</v>
+        <v>0.00686468742787838</v>
       </c>
       <c r="C41" s="1">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2972,16 +2630,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.114407129585743</v>
+        <v>0.006101944483816624</v>
       </c>
       <c r="C42" s="1">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2998,16 +2656,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.1111383512616158</v>
+        <v>0.005339201539754868</v>
       </c>
       <c r="C43" s="1">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3024,16 +2682,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.1078695729374886</v>
+        <v>0.005339201539754868</v>
       </c>
       <c r="C44" s="1">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3050,16 +2708,16 @@
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.08498814702033997</v>
+        <v>0.00495783006772399</v>
       </c>
       <c r="C45" s="1">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3076,16 +2734,16 @@
         <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.08498814702033997</v>
+        <v>0.00495783006772399</v>
       </c>
       <c r="C46" s="1">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3102,16 +2760,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.08171937614679337</v>
+        <v>0.004576458130031824</v>
       </c>
       <c r="C47" s="1">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3128,16 +2786,16 @@
         <v>48</v>
       </c>
       <c r="B48" s="2">
-        <v>0.08171937614679337</v>
+        <v>0.004195086658000946</v>
       </c>
       <c r="C48" s="1">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3154,16 +2812,16 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.07845059782266617</v>
+        <v>0.00343234371393919</v>
       </c>
       <c r="C49" s="1">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3180,16 +2838,16 @@
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.07845059782266617</v>
+        <v>0.003050972241908312</v>
       </c>
       <c r="C50" s="1">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3206,16 +2864,16 @@
         <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.07845059782266617</v>
+        <v>0.003050972241908312</v>
       </c>
       <c r="C51" s="1">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3232,16 +2890,16 @@
         <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>0.07191304862499237</v>
+        <v>0.002669600769877434</v>
       </c>
       <c r="C52" s="1">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3258,16 +2916,16 @@
         <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>0.07191304862499237</v>
+        <v>0.002669600769877434</v>
       </c>
       <c r="C53" s="1">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3284,16 +2942,16 @@
         <v>54</v>
       </c>
       <c r="B54" s="2">
-        <v>0.07191304862499237</v>
+        <v>0.002669600769877434</v>
       </c>
       <c r="C54" s="1">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3310,16 +2968,16 @@
         <v>55</v>
       </c>
       <c r="B55" s="2">
-        <v>0.06537549942731857</v>
+        <v>0.002669600769877434</v>
       </c>
       <c r="C55" s="1">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3336,16 +2994,16 @@
         <v>56</v>
       </c>
       <c r="B56" s="2">
-        <v>0.05883795022964478</v>
+        <v>0.002288229065015912</v>
       </c>
       <c r="C56" s="1">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3359,45 +3017,45 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>0.05883795022964478</v>
+        <v>0.002288229065015912</v>
       </c>
       <c r="C57" s="1">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="D57" s="1">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="E57" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.05556917563080788</v>
+        <v>0.002288229065015912</v>
       </c>
       <c r="C58" s="1">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3411,19 +3069,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2">
-        <v>0.05230040103197098</v>
+        <v>0.002288229065015912</v>
       </c>
       <c r="C59" s="1">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3437,19 +3095,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2">
-        <v>0.04576285183429718</v>
+        <v>0.001906857592985034</v>
       </c>
       <c r="C60" s="1">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3463,19 +3121,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2">
-        <v>0.04576285183429718</v>
+        <v>0.001906857592985034</v>
       </c>
       <c r="C61" s="1">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3489,19 +3147,19 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" s="2">
-        <v>0.04249407351016998</v>
+        <v>0.001525486120954156</v>
       </c>
       <c r="C62" s="1">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3515,19 +3173,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="B63" s="2">
-        <v>0.04249407351016998</v>
+        <v>0.001525486120954156</v>
       </c>
       <c r="C63" s="1">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E63" s="1">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3536,24 +3194,24 @@
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.03922529891133308</v>
+        <v>0.001525486120954156</v>
       </c>
       <c r="C64" s="1">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3567,19 +3225,19 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.02941897511482239</v>
+        <v>0.001525486120954156</v>
       </c>
       <c r="C65" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3593,19 +3251,19 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.02615020051598549</v>
+        <v>0.001144114532507956</v>
       </c>
       <c r="C66" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3619,19 +3277,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.02615020051598549</v>
+        <v>0.001144114532507956</v>
       </c>
       <c r="C67" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3645,19 +3303,19 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.02288142591714859</v>
+        <v>0.001144114532507956</v>
       </c>
       <c r="C68" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3671,19 +3329,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.02288142591714859</v>
+        <v>0.001144114532507956</v>
       </c>
       <c r="C69" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3697,19 +3355,19 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.02288142591714859</v>
+        <v>0.001144114532507956</v>
       </c>
       <c r="C70" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3723,19 +3381,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>0.02288142591714859</v>
+        <v>0.001144114532507956</v>
       </c>
       <c r="C71" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3749,19 +3407,19 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>0.01961264945566654</v>
+        <v>0.000762743060477078</v>
       </c>
       <c r="C72" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3775,45 +3433,45 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.000762743060477078</v>
+      </c>
+      <c r="C73" s="1">
         <v>4</v>
       </c>
-      <c r="B73" s="2">
-        <v>0.01961264945566654</v>
-      </c>
-      <c r="C73" s="1">
-        <v>12</v>
-      </c>
       <c r="D73" s="1">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>0.01961264945566654</v>
+        <v>0.000381371530238539</v>
       </c>
       <c r="C74" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -3827,19 +3485,19 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>0.01961264945566654</v>
+        <v>0.000381371530238539</v>
       </c>
       <c r="C75" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -3853,19 +3511,19 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>0.01634387485682964</v>
+        <v>0.000381371530238539</v>
       </c>
       <c r="C76" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -3879,19 +3537,19 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>0.01634387485682964</v>
+        <v>0.000381371530238539</v>
       </c>
       <c r="C77" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -3904,1022 +3562,34 @@
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="2">
-        <v>0.01634387485682964</v>
-      </c>
-      <c r="C78" s="1">
-        <v>10</v>
-      </c>
-      <c r="D78" s="1">
-        <v>0</v>
-      </c>
-      <c r="E78" s="1">
-        <v>10</v>
-      </c>
-      <c r="F78" s="1">
-        <v>0</v>
-      </c>
-      <c r="G78" s="1">
-        <v>0</v>
-      </c>
-      <c r="H78" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2">
-        <v>0.01634387485682964</v>
-      </c>
-      <c r="C79" s="1">
-        <v>10</v>
-      </c>
-      <c r="D79" s="1">
-        <v>0</v>
-      </c>
-      <c r="E79" s="1">
-        <v>10</v>
-      </c>
-      <c r="F79" s="1">
-        <v>0</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0</v>
-      </c>
-      <c r="H79" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2">
-        <v>0.01307510025799274</v>
-      </c>
-      <c r="C80" s="1">
-        <v>8</v>
-      </c>
-      <c r="D80" s="1">
-        <v>0</v>
-      </c>
-      <c r="E80" s="1">
-        <v>8</v>
-      </c>
-      <c r="F80" s="1">
-        <v>0</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0</v>
-      </c>
-      <c r="H80" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2">
-        <v>0.01307510025799274</v>
-      </c>
-      <c r="C81" s="1">
-        <v>8</v>
-      </c>
-      <c r="D81" s="1">
-        <v>0</v>
-      </c>
-      <c r="E81" s="1">
-        <v>8</v>
-      </c>
-      <c r="F81" s="1">
-        <v>0</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0</v>
-      </c>
-      <c r="H81" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B82" s="2">
-        <v>0.01307510025799274</v>
-      </c>
-      <c r="C82" s="1">
-        <v>8</v>
-      </c>
-      <c r="D82" s="1">
-        <v>96</v>
-      </c>
-      <c r="E82" s="1">
-        <v>8</v>
-      </c>
-      <c r="F82" s="1">
-        <v>0</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0</v>
-      </c>
-      <c r="H82" s="1">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B83" s="2">
-        <v>0.01307510025799274</v>
-      </c>
-      <c r="C83" s="1">
-        <v>8</v>
-      </c>
-      <c r="D83" s="1">
-        <v>0</v>
-      </c>
-      <c r="E83" s="1">
-        <v>8</v>
-      </c>
-      <c r="F83" s="1">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1">
-        <v>0</v>
-      </c>
-      <c r="H83" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B84" s="2">
-        <v>0.01307510025799274</v>
-      </c>
-      <c r="C84" s="1">
-        <v>8</v>
-      </c>
-      <c r="D84" s="1">
-        <v>0</v>
-      </c>
-      <c r="E84" s="1">
-        <v>8</v>
-      </c>
-      <c r="F84" s="1">
-        <v>0</v>
-      </c>
-      <c r="G84" s="1">
-        <v>0</v>
-      </c>
-      <c r="H84" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B85" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C85" s="1">
-        <v>6</v>
-      </c>
-      <c r="D85" s="1">
-        <v>0</v>
-      </c>
-      <c r="E85" s="1">
-        <v>6</v>
-      </c>
-      <c r="F85" s="1">
-        <v>0</v>
-      </c>
-      <c r="G85" s="1">
-        <v>0</v>
-      </c>
-      <c r="H85" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B86" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C86" s="1">
-        <v>6</v>
-      </c>
-      <c r="D86" s="1">
-        <v>0</v>
-      </c>
-      <c r="E86" s="1">
-        <v>6</v>
-      </c>
-      <c r="F86" s="1">
-        <v>0</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0</v>
-      </c>
-      <c r="H86" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B87" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C87" s="1">
-        <v>6</v>
-      </c>
-      <c r="D87" s="1">
-        <v>0</v>
-      </c>
-      <c r="E87" s="1">
-        <v>6</v>
-      </c>
-      <c r="F87" s="1">
-        <v>0</v>
-      </c>
-      <c r="G87" s="1">
-        <v>0</v>
-      </c>
-      <c r="H87" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B88" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C88" s="1">
-        <v>6</v>
-      </c>
-      <c r="D88" s="1">
-        <v>0</v>
-      </c>
-      <c r="E88" s="1">
-        <v>6</v>
-      </c>
-      <c r="F88" s="1">
-        <v>0</v>
-      </c>
-      <c r="G88" s="1">
-        <v>0</v>
-      </c>
-      <c r="H88" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B89" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C89" s="1">
-        <v>6</v>
-      </c>
-      <c r="D89" s="1">
-        <v>0</v>
-      </c>
-      <c r="E89" s="1">
-        <v>6</v>
-      </c>
-      <c r="F89" s="1">
-        <v>0</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0</v>
-      </c>
-      <c r="H89" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B90" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C90" s="1">
-        <v>6</v>
-      </c>
-      <c r="D90" s="1">
-        <v>0</v>
-      </c>
-      <c r="E90" s="1">
-        <v>6</v>
-      </c>
-      <c r="F90" s="1">
-        <v>0</v>
-      </c>
-      <c r="G90" s="1">
-        <v>0</v>
-      </c>
-      <c r="H90" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B91" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C91" s="1">
-        <v>6</v>
-      </c>
-      <c r="D91" s="1">
-        <v>0</v>
-      </c>
-      <c r="E91" s="1">
-        <v>6</v>
-      </c>
-      <c r="F91" s="1">
-        <v>0</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0</v>
-      </c>
-      <c r="H91" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B92" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C92" s="1">
-        <v>6</v>
-      </c>
-      <c r="D92" s="1">
-        <v>0</v>
-      </c>
-      <c r="E92" s="1">
-        <v>6</v>
-      </c>
-      <c r="F92" s="1">
-        <v>0</v>
-      </c>
-      <c r="G92" s="1">
-        <v>0</v>
-      </c>
-      <c r="H92" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B93" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C93" s="1">
-        <v>6</v>
-      </c>
-      <c r="D93" s="1">
-        <v>0</v>
-      </c>
-      <c r="E93" s="1">
-        <v>6</v>
-      </c>
-      <c r="F93" s="1">
-        <v>0</v>
-      </c>
-      <c r="G93" s="1">
-        <v>0</v>
-      </c>
-      <c r="H93" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B94" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C94" s="1">
-        <v>6</v>
-      </c>
-      <c r="D94" s="1">
-        <v>0</v>
-      </c>
-      <c r="E94" s="1">
-        <v>6</v>
-      </c>
-      <c r="F94" s="1">
-        <v>0</v>
-      </c>
-      <c r="G94" s="1">
-        <v>0</v>
-      </c>
-      <c r="H94" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B95" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C95" s="1">
-        <v>6</v>
-      </c>
-      <c r="D95" s="1">
-        <v>0</v>
-      </c>
-      <c r="E95" s="1">
-        <v>6</v>
-      </c>
-      <c r="F95" s="1">
-        <v>0</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0</v>
-      </c>
-      <c r="H95" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B96" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C96" s="1">
-        <v>6</v>
-      </c>
-      <c r="D96" s="1">
-        <v>0</v>
-      </c>
-      <c r="E96" s="1">
-        <v>6</v>
-      </c>
-      <c r="F96" s="1">
-        <v>0</v>
-      </c>
-      <c r="G96" s="1">
-        <v>0</v>
-      </c>
-      <c r="H96" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B97" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C97" s="1">
-        <v>6</v>
-      </c>
-      <c r="D97" s="1">
-        <v>0</v>
-      </c>
-      <c r="E97" s="1">
-        <v>6</v>
-      </c>
-      <c r="F97" s="1">
-        <v>0</v>
-      </c>
-      <c r="G97" s="1">
-        <v>0</v>
-      </c>
-      <c r="H97" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B98" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C98" s="1">
-        <v>6</v>
-      </c>
-      <c r="D98" s="1">
-        <v>0</v>
-      </c>
-      <c r="E98" s="1">
-        <v>6</v>
-      </c>
-      <c r="F98" s="1">
-        <v>0</v>
-      </c>
-      <c r="G98" s="1">
-        <v>0</v>
-      </c>
-      <c r="H98" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B99" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C99" s="1">
-        <v>6</v>
-      </c>
-      <c r="D99" s="1">
-        <v>0</v>
-      </c>
-      <c r="E99" s="1">
-        <v>6</v>
-      </c>
-      <c r="F99" s="1">
-        <v>0</v>
-      </c>
-      <c r="G99" s="1">
-        <v>0</v>
-      </c>
-      <c r="H99" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B100" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C100" s="1">
-        <v>6</v>
-      </c>
-      <c r="D100" s="1">
-        <v>0</v>
-      </c>
-      <c r="E100" s="1">
-        <v>6</v>
-      </c>
-      <c r="F100" s="1">
-        <v>0</v>
-      </c>
-      <c r="G100" s="1">
-        <v>0</v>
-      </c>
-      <c r="H100" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B101" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C101" s="1">
-        <v>6</v>
-      </c>
-      <c r="D101" s="1">
-        <v>0</v>
-      </c>
-      <c r="E101" s="1">
-        <v>6</v>
-      </c>
-      <c r="F101" s="1">
-        <v>0</v>
-      </c>
-      <c r="G101" s="1">
-        <v>0</v>
-      </c>
-      <c r="H101" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B102" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C102" s="1">
-        <v>6</v>
-      </c>
-      <c r="D102" s="1">
-        <v>0</v>
-      </c>
-      <c r="E102" s="1">
-        <v>6</v>
-      </c>
-      <c r="F102" s="1">
-        <v>0</v>
-      </c>
-      <c r="G102" s="1">
-        <v>0</v>
-      </c>
-      <c r="H102" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B103" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C103" s="1">
-        <v>6</v>
-      </c>
-      <c r="D103" s="1">
-        <v>0</v>
-      </c>
-      <c r="E103" s="1">
-        <v>6</v>
-      </c>
-      <c r="F103" s="1">
-        <v>0</v>
-      </c>
-      <c r="G103" s="1">
-        <v>0</v>
-      </c>
-      <c r="H103" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B104" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C104" s="1">
-        <v>6</v>
-      </c>
-      <c r="D104" s="1">
-        <v>0</v>
-      </c>
-      <c r="E104" s="1">
-        <v>6</v>
-      </c>
-      <c r="F104" s="1">
-        <v>0</v>
-      </c>
-      <c r="G104" s="1">
-        <v>0</v>
-      </c>
-      <c r="H104" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B105" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C105" s="1">
-        <v>6</v>
-      </c>
-      <c r="D105" s="1">
-        <v>0</v>
-      </c>
-      <c r="E105" s="1">
-        <v>6</v>
-      </c>
-      <c r="F105" s="1">
-        <v>0</v>
-      </c>
-      <c r="G105" s="1">
-        <v>0</v>
-      </c>
-      <c r="H105" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B106" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C106" s="1">
-        <v>6</v>
-      </c>
-      <c r="D106" s="1">
-        <v>0</v>
-      </c>
-      <c r="E106" s="1">
-        <v>6</v>
-      </c>
-      <c r="F106" s="1">
-        <v>0</v>
-      </c>
-      <c r="G106" s="1">
-        <v>0</v>
-      </c>
-      <c r="H106" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B107" s="2">
-        <v>0.009806324727833271</v>
-      </c>
-      <c r="C107" s="1">
-        <v>6</v>
-      </c>
-      <c r="D107" s="1">
-        <v>0</v>
-      </c>
-      <c r="E107" s="1">
-        <v>6</v>
-      </c>
-      <c r="F107" s="1">
-        <v>0</v>
-      </c>
-      <c r="G107" s="1">
-        <v>0</v>
-      </c>
-      <c r="H107" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B108" s="2">
-        <v>0.006537550128996372</v>
-      </c>
-      <c r="C108" s="1">
-        <v>4</v>
-      </c>
-      <c r="D108" s="1">
-        <v>0</v>
-      </c>
-      <c r="E108" s="1">
-        <v>4</v>
-      </c>
-      <c r="F108" s="1">
-        <v>0</v>
-      </c>
-      <c r="G108" s="1">
-        <v>0</v>
-      </c>
-      <c r="H108" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B109" s="2">
-        <v>0.006537550128996372</v>
-      </c>
-      <c r="C109" s="1">
-        <v>4</v>
-      </c>
-      <c r="D109" s="1">
-        <v>0</v>
-      </c>
-      <c r="E109" s="1">
-        <v>4</v>
-      </c>
-      <c r="F109" s="1">
-        <v>0</v>
-      </c>
-      <c r="G109" s="1">
-        <v>0</v>
-      </c>
-      <c r="H109" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B110" s="2">
-        <v>0.006537550128996372</v>
-      </c>
-      <c r="C110" s="1">
-        <v>4</v>
-      </c>
-      <c r="D110" s="1">
-        <v>0</v>
-      </c>
-      <c r="E110" s="1">
-        <v>4</v>
-      </c>
-      <c r="F110" s="1">
-        <v>0</v>
-      </c>
-      <c r="G110" s="1">
-        <v>0</v>
-      </c>
-      <c r="H110" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B111" s="2">
-        <v>0.006537550128996372</v>
-      </c>
-      <c r="C111" s="1">
-        <v>4</v>
-      </c>
-      <c r="D111" s="1">
-        <v>0</v>
-      </c>
-      <c r="E111" s="1">
-        <v>4</v>
-      </c>
-      <c r="F111" s="1">
-        <v>0</v>
-      </c>
-      <c r="G111" s="1">
-        <v>0</v>
-      </c>
-      <c r="H111" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B112" s="2">
-        <v>0.003268775064498186</v>
-      </c>
-      <c r="C112" s="1">
-        <v>2</v>
-      </c>
-      <c r="D112" s="1">
-        <v>0</v>
-      </c>
-      <c r="E112" s="1">
-        <v>2</v>
-      </c>
-      <c r="F112" s="1">
-        <v>0</v>
-      </c>
-      <c r="G112" s="1">
-        <v>0</v>
-      </c>
-      <c r="H112" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B113" s="2">
-        <v>0.003268775064498186</v>
-      </c>
-      <c r="C113" s="1">
-        <v>2</v>
-      </c>
-      <c r="D113" s="1">
-        <v>0</v>
-      </c>
-      <c r="E113" s="1">
-        <v>2</v>
-      </c>
-      <c r="F113" s="1">
-        <v>0</v>
-      </c>
-      <c r="G113" s="1">
-        <v>0</v>
-      </c>
-      <c r="H113" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B114" s="2">
-        <v>0.003268775064498186</v>
-      </c>
-      <c r="C114" s="1">
-        <v>2</v>
-      </c>
-      <c r="D114" s="1">
-        <v>0</v>
-      </c>
-      <c r="E114" s="1">
-        <v>2</v>
-      </c>
-      <c r="F114" s="1">
-        <v>0</v>
-      </c>
-      <c r="G114" s="1">
-        <v>0</v>
-      </c>
-      <c r="H114" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B115" s="2">
-        <v>0.003268775064498186</v>
-      </c>
-      <c r="C115" s="1">
-        <v>2</v>
-      </c>
-      <c r="D115" s="1">
-        <v>0</v>
-      </c>
-      <c r="E115" s="1">
-        <v>2</v>
-      </c>
-      <c r="F115" s="1">
-        <v>0</v>
-      </c>
-      <c r="G115" s="1">
-        <v>0</v>
-      </c>
-      <c r="H115" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" t="s">
-        <v>115</v>
-      </c>
-      <c r="B116">
+      <c r="B78">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C116">
+      <c r="C78">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D116">
+      <c r="D78">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E116">
+      <c r="E78">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F116">
+      <c r="F78">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G116">
+      <c r="G78">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H116">
+      <c r="H78">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/AT32 FOR LVGL/app/project/MDK_V5/AT32F403AVGT7_WorkBench_analysis.xlsx
+++ b/AT32 FOR LVGL/app/project/MDK_V5/AT32F403AVGT7_WorkBench_analysis.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
   <si>
     <t>AT32F403AVGT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-5e356c.o</t>
+    <t>lto-llvm-d426df.o</t>
   </si>
   <si>
     <t>startup_at32f403a_407.o</t>
@@ -38,9 +38,6 @@
     <t>flsbuf.o</t>
   </si>
   <si>
-    <t>__printf_flags_wp.o</t>
-  </si>
-  <si>
     <t>initio.o</t>
   </si>
   <si>
@@ -56,24 +53,15 @@
     <t>fopen.o</t>
   </si>
   <si>
-    <t>_printf_intcommon.o</t>
-  </si>
-  <si>
     <t>rt_memcpy_v6.o</t>
   </si>
   <si>
     <t>init_alloc.o</t>
   </si>
   <si>
-    <t>_printf_hex_int.o</t>
-  </si>
-  <si>
     <t>strcmpv7em.o</t>
   </si>
   <si>
-    <t>_printf_dec.o</t>
-  </si>
-  <si>
     <t>llsdiv.o</t>
   </si>
   <si>
@@ -98,9 +86,6 @@
     <t>h1_free.o</t>
   </si>
   <si>
-    <t>_printf_pad.o</t>
-  </si>
-  <si>
     <t>fclose.o</t>
   </si>
   <si>
@@ -131,18 +116,12 @@
     <t>defsig_general.o</t>
   </si>
   <si>
-    <t>_printf_char_common.o</t>
-  </si>
-  <si>
     <t>puts.o</t>
   </si>
   <si>
     <t>init_aeabi.o</t>
   </si>
   <si>
-    <t>_printf_char_file.o</t>
-  </si>
-  <si>
     <t>systick_wrapper_gnu.o</t>
   </si>
   <si>
@@ -158,9 +137,6 @@
     <t>fpinit.o</t>
   </si>
   <si>
-    <t>noretval__2printf.o</t>
-  </si>
-  <si>
     <t>libinit2.o</t>
   </si>
   <si>
@@ -182,9 +158,6 @@
     <t>defsig_rtmem_outer.o</t>
   </si>
   <si>
-    <t>__printf_wp.o</t>
-  </si>
-  <si>
     <t>sys_exit.o</t>
   </si>
   <si>
@@ -203,9 +176,6 @@
     <t>rt_errno_addr_intlibspace.o</t>
   </si>
   <si>
-    <t>ferror.o</t>
-  </si>
-  <si>
     <t>__main.o</t>
   </si>
   <si>
@@ -215,22 +185,10 @@
     <t>heapauxi.o</t>
   </si>
   <si>
-    <t>_printf_x.o</t>
-  </si>
-  <si>
-    <t>_printf_u.o</t>
-  </si>
-  <si>
-    <t>_printf_d.o</t>
-  </si>
-  <si>
     <t>__rtentry4.o</t>
   </si>
   <si>
     <t>hguard.o</t>
-  </si>
-  <si>
-    <t>_printf_percent_end.o</t>
   </si>
   <si>
     <t>use_no_semi.o</t>
@@ -362,11 +320,11 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$78</c:f>
+              <c:f>ram_percent!$A$3:$A$64</c:f>
               <c:strCache>
-                <c:ptCount val="76"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-5e356c.o</c:v>
+                  <c:v>lto-llvm-d426df.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f403a_407.o</c:v>
@@ -380,7 +338,7 @@
                 <c:pt idx="4">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="61">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -388,26 +346,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$78</c:f>
+              <c:f>ram_percent!$B$3:$B$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>98.70268249511719</c:v>
+                  <c:v>98.33460998535156</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8832814693450928</c:v>
+                  <c:v>1.133880615234375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2070190906524658</c:v>
+                  <c:v>0.2657532691955566</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1518139988183975</c:v>
+                  <c:v>0.1948857307434082</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0552050918340683</c:v>
-                </c:pt>
-                <c:pt idx="75">
+                  <c:v>0.07086753845214844</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -475,11 +433,11 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$78</c:f>
+              <c:f>flash_percent!$A$3:$A$64</c:f>
               <c:strCache>
-                <c:ptCount val="76"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-5e356c.o</c:v>
+                  <c:v>lto-llvm-d426df.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>c_w.l</c:v>
@@ -491,219 +449,177 @@
                   <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>__printf_flags_wp.o</c:v>
+                  <c:v>initio.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>initio.o</c:v>
+                  <c:v>stdio.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>stdio.o</c:v>
+                  <c:v>fseek.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>fseek.o</c:v>
+                  <c:v>lludivv7m.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>lludivv7m.o</c:v>
+                  <c:v>fopen.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>fopen.o</c:v>
+                  <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>_printf_intcommon.o</c:v>
+                  <c:v>init_alloc.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>rt_memcpy_v6.o</c:v>
+                  <c:v>strcmpv7em.o</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>init_alloc.o</c:v>
+                  <c:v>llsdiv.o</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>_printf_hex_int.o</c:v>
+                  <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>strcmpv7em.o</c:v>
+                  <c:v>h1_alloc.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>_printf_dec.o</c:v>
+                  <c:v>__scatter.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>llsdiv.o</c:v>
+                  <c:v>__dczerorl2.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>rt_memcpy_w.o</c:v>
+                  <c:v>defsig_rtmem_inner.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>h1_alloc.o</c:v>
+                  <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>__scatter.o</c:v>
+                  <c:v>h1_free.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>__dczerorl2.o</c:v>
+                  <c:v>fclose.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>defsig_rtmem_inner.o</c:v>
+                  <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>rt_memclr_w.o</c:v>
+                  <c:v>strcpy.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>h1_free.o</c:v>
+                  <c:v>setvbuf.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>_printf_pad.o</c:v>
+                  <c:v>rt_memclr.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>fclose.o</c:v>
+                  <c:v>ftell.o</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>sys_stackheap_outer.o</c:v>
+                  <c:v>strlen.o</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>strcpy.o</c:v>
+                  <c:v>h1_extend.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>setvbuf.o</c:v>
+                  <c:v>defsig_rtred_inner.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>rt_memclr.o</c:v>
+                  <c:v>defsig_general.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>ftell.o</c:v>
+                  <c:v>puts.o</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>strlen.o</c:v>
+                  <c:v>init_aeabi.o</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>h1_extend.o</c:v>
+                  <c:v>systick_wrapper_gnu.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>defsig_rtred_inner.o</c:v>
+                  <c:v>fputc.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>defsig_general.o</c:v>
+                  <c:v>__scatter_zi.o</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>_printf_char_common.o</c:v>
+                  <c:v>fz_wm.l</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>puts.o</c:v>
+                  <c:v>fpinit.o</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>init_aeabi.o</c:v>
+                  <c:v>libinit2.o</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>_printf_char_file.o</c:v>
+                  <c:v>exit.o</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>systick_wrapper_gnu.o</c:v>
+                  <c:v>aeabi_memset4.o</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>fputc.o</c:v>
+                  <c:v>aeabi_memset.o</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>__scatter_zi.o</c:v>
+                  <c:v>sys_wrch.o</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>fz_wm.l</c:v>
+                  <c:v>defsig_rtred_outer.o</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>fpinit.o</c:v>
+                  <c:v>defsig_rtmem_outer.o</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>noretval__2printf.o</c:v>
+                  <c:v>sys_exit.o</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>libinit2.o</c:v>
+                  <c:v>stdio_streams.o</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>exit.o</c:v>
+                  <c:v>h1_init.o</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>aeabi_memset4.o</c:v>
+                  <c:v>__rtentry2.o</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>aeabi_memset.o</c:v>
+                  <c:v>rtexit2.o</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>sys_wrch.o</c:v>
+                  <c:v>defsig_exit.o</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>defsig_rtred_outer.o</c:v>
+                  <c:v>rt_errno_addr_intlibspace.o</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>defsig_rtmem_outer.o</c:v>
+                  <c:v>libspace.o</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>__printf_wp.o</c:v>
+                  <c:v>__main.o</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>sys_exit.o</c:v>
+                  <c:v>libshutdown2.o</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>stdio_streams.o</c:v>
+                  <c:v>heapauxi.o</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>h1_init.o</c:v>
+                  <c:v>__rtentry4.o</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>__rtentry2.o</c:v>
+                  <c:v>hguard.o</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>rtexit2.o</c:v>
+                  <c:v>use_no_semi.o</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>defsig_exit.o</c:v>
+                  <c:v>rtexit.o</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>rt_errno_addr_intlibspace.o</c:v>
+                  <c:v>libshutdown.o</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>libspace.o</c:v>
+                  <c:v>libinit.o</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>ferror.o</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>__main.o</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>libshutdown2.o</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>heapauxi.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>_printf_x.o</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>_printf_u.o</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>_printf_d.o</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>__rtentry4.o</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>hguard.o</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>_printf_percent_end.o</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>use_no_semi.o</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>rtexit.o</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>libshutdown.o</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>libinit.o</c:v>
-                </c:pt>
-                <c:pt idx="75">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -711,236 +627,194 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$78</c:f>
+              <c:f>flash_percent!$B$3:$B$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>98.01877593994141</c:v>
+                  <c:v>98.38481140136719</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9402714967727661</c:v>
+                  <c:v>0.7569523453712463</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.09191054105758667</c:v>
+                  <c:v>0.09246097505092621</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.08618996292352676</c:v>
+                  <c:v>0.08670614659786224</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.06273561716079712</c:v>
+                  <c:v>0.05985026061534882</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.05949395895004273</c:v>
+                  <c:v>0.05064252763986588</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.05034103989601135</c:v>
+                  <c:v>0.0475732833147049</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.04729006811976433</c:v>
+                  <c:v>0.04603866115212441</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.04576458409428597</c:v>
+                  <c:v>0.04603866115212441</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.04576458409428597</c:v>
+                  <c:v>0.02647222951054573</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.03394206613302231</c:v>
+                  <c:v>0.02647222951054573</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.0263146348297596</c:v>
+                  <c:v>0.02378664165735245</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.0263146348297596</c:v>
+                  <c:v>0.02225201949477196</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.0244077779352665</c:v>
+                  <c:v>0.01918277516961098</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.02364503405988216</c:v>
+                  <c:v>0.01803180947899818</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.02288229204714298</c:v>
+                  <c:v>0.01803180947899818</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.02211954817175865</c:v>
+                  <c:v>0.01726449839770794</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.01906857639551163</c:v>
+                  <c:v>0.01534622069448233</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.01792446151375771</c:v>
+                  <c:v>0.0149625651538372</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.01792446151375771</c:v>
+                  <c:v>0.0149625651538372</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.01716171950101852</c:v>
+                  <c:v>0.01457890961319208</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.01525486074388027</c:v>
+                  <c:v>0.01419525407254696</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.01487348973751068</c:v>
+                  <c:v>0.01381159853190184</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.01487348973751068</c:v>
+                  <c:v>0.01342794299125671</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.01487348973751068</c:v>
+                  <c:v>0.01304428745061159</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.01449211779981852</c:v>
+                  <c:v>0.01266063190996647</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.01411074679344893</c:v>
+                  <c:v>0.01189332082867622</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.01372937485575676</c:v>
+                  <c:v>0.009975043125450611</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.01334800384938717</c:v>
+                  <c:v>0.009975043125450611</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.012966631911695</c:v>
+                  <c:v>0.009591387584805489</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.01258525997400284</c:v>
+                  <c:v>0.008440420962870121</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01182251702994108</c:v>
+                  <c:v>0.008440420962870121</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.009915660135447979</c:v>
+                  <c:v>0.006138488184660673</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.009915660135447979</c:v>
+                  <c:v>0.005371177103370428</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.009534288197755814</c:v>
+                  <c:v>0.005371177103370428</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.009152916260063648</c:v>
+                  <c:v>0.004987521562725306</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.008390173316001892</c:v>
+                  <c:v>0.004987521562725306</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.008390173316001892</c:v>
+                  <c:v>0.004220210481435061</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.00686468742787838</c:v>
+                  <c:v>0.003452899632975459</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.006101944483816624</c:v>
+                  <c:v>0.003069244092330337</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.005339201539754868</c:v>
+                  <c:v>0.003069244092330337</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.005339201539754868</c:v>
+                  <c:v>0.002685588551685214</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.00495783006772399</c:v>
+                  <c:v>0.002685588551685214</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.00495783006772399</c:v>
+                  <c:v>0.002685588551685214</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.004576458130031824</c:v>
+                  <c:v>0.002301933011040092</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.004195086658000946</c:v>
+                  <c:v>0.002301933011040092</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.00343234371393919</c:v>
+                  <c:v>0.002301933011040092</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.003050972241908312</c:v>
+                  <c:v>0.002301933011040092</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.003050972241908312</c:v>
+                  <c:v>0.001918277586810291</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.002669600769877434</c:v>
+                  <c:v>0.001918277586810291</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.002669600769877434</c:v>
+                  <c:v>0.001534622046165168</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.002669600769877434</c:v>
+                  <c:v>0.001534622046165168</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.002669600769877434</c:v>
+                  <c:v>0.001534622046165168</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.002288229065015912</c:v>
+                  <c:v>0.001150966505520046</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.002288229065015912</c:v>
+                  <c:v>0.001150966505520046</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.002288229065015912</c:v>
+                  <c:v>0.001150966505520046</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.002288229065015912</c:v>
+                  <c:v>0.0007673110230825841</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.001906857592985034</c:v>
+                  <c:v>0.0003836555115412921</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.001906857592985034</c:v>
+                  <c:v>0.0003836555115412921</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.001525486120954156</c:v>
+                  <c:v>0.0003836555115412921</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.001525486120954156</c:v>
+                  <c:v>0.0003836555115412921</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.001525486120954156</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.001525486120954156</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.001144114532507956</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.001144114532507956</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.001144114532507956</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.001144114532507956</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.001144114532507956</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.001144114532507956</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.000762743060477078</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.000762743060477078</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.000381371530238539</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.000381371530238539</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.000381371530238539</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.000381371530238539</c:v>
-                </c:pt>
-                <c:pt idx="75">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1045,8 +919,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H78" totalsRowCount="1">
-  <autoFilter ref="A2:H77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H64" totalsRowCount="1">
+  <autoFilter ref="A2:H63"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1062,8 +936,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H78" totalsRowCount="1">
-  <autoFilter ref="A2:H77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H64" totalsRowCount="1">
+  <autoFilter ref="A2:H63"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1363,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1376,28 +1250,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1405,25 +1279,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>98.70268249511719</v>
+        <v>98.33460998535156</v>
       </c>
       <c r="C3" s="1">
-        <v>171641</v>
+        <v>133208</v>
       </c>
       <c r="D3" s="1">
-        <v>514033</v>
+        <v>512881</v>
       </c>
       <c r="E3" s="1">
-        <v>381842</v>
+        <v>380766</v>
       </c>
       <c r="F3" s="1">
-        <v>131803</v>
+        <v>131727</v>
       </c>
       <c r="G3" s="1">
         <v>388</v>
       </c>
       <c r="H3" s="1">
-        <v>171253</v>
+        <v>132820</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1431,7 +1305,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>0.8832814693450928</v>
+        <v>1.133880615234375</v>
       </c>
       <c r="C4" s="1">
         <v>1536</v>
@@ -1457,19 +1331,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>0.2070190906524658</v>
+        <v>0.2657532691955566</v>
       </c>
       <c r="C5" s="1">
         <v>360</v>
       </c>
       <c r="D5" s="1">
-        <v>4931</v>
+        <v>3946</v>
       </c>
       <c r="E5" s="1">
-        <v>4862</v>
+        <v>3934</v>
       </c>
       <c r="F5" s="1">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
         <v>12</v>
@@ -1483,7 +1357,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.1518139988183975</v>
+        <v>0.1948857307434082</v>
       </c>
       <c r="C6" s="1">
         <v>264</v>
@@ -1509,7 +1383,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.0552050918340683</v>
+        <v>0.07086753845214844</v>
       </c>
       <c r="C7" s="1">
         <v>96</v>
@@ -1530,35 +1404,35 @@
         <v>96</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-      <c r="B78">
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C78">
+      <c r="C64">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D78">
+      <c r="D64">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E78">
+      <c r="E64">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F78">
+      <c r="F64">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G78">
+      <c r="G64">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H78">
+      <c r="H64">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1574,7 +1448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1587,28 +1461,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1616,25 +1490,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>98.01877593994141</v>
+        <v>98.38481140136719</v>
       </c>
       <c r="C3" s="1">
-        <v>514033</v>
+        <v>512881</v>
       </c>
       <c r="D3" s="1">
-        <v>171641</v>
+        <v>133208</v>
       </c>
       <c r="E3" s="1">
-        <v>381842</v>
+        <v>380766</v>
       </c>
       <c r="F3" s="1">
-        <v>131803</v>
+        <v>131727</v>
       </c>
       <c r="G3" s="1">
         <v>388</v>
       </c>
       <c r="H3" s="1">
-        <v>171253</v>
+        <v>132820</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1642,19 +1516,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>0.9402714967727661</v>
+        <v>0.7569523453712463</v>
       </c>
       <c r="C4" s="1">
-        <v>4931</v>
+        <v>3946</v>
       </c>
       <c r="D4" s="1">
         <v>360</v>
       </c>
       <c r="E4" s="1">
-        <v>4862</v>
+        <v>3934</v>
       </c>
       <c r="F4" s="1">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
         <v>12</v>
@@ -1668,7 +1542,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>0.09191054105758667</v>
+        <v>0.09246097505092621</v>
       </c>
       <c r="C5" s="1">
         <v>482</v>
@@ -1694,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>0.08618996292352676</v>
+        <v>0.08670614659786224</v>
       </c>
       <c r="C6" s="1">
         <v>452</v>
@@ -1720,10 +1594,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>0.06273561716079712</v>
+        <v>0.05985026061534882</v>
       </c>
       <c r="C7" s="1">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -1732,7 +1606,7 @@
         <v>312</v>
       </c>
       <c r="F7" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1746,16 +1620,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.05949395895004273</v>
+        <v>0.05064252763986588</v>
       </c>
       <c r="C8" s="1">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1772,16 +1646,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>0.05034103989601135</v>
+        <v>0.0475732833147049</v>
       </c>
       <c r="C9" s="1">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1798,16 +1672,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>0.04729006811976433</v>
+        <v>0.04603866115212441</v>
       </c>
       <c r="C10" s="1">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1824,7 +1698,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>0.04576458409428597</v>
+        <v>0.04603866115212441</v>
       </c>
       <c r="C11" s="1">
         <v>240</v>
@@ -1850,16 +1724,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>0.04576458409428597</v>
+        <v>0.02647222951054573</v>
       </c>
       <c r="C12" s="1">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1876,16 +1750,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>0.03394206613302231</v>
+        <v>0.02647222951054573</v>
       </c>
       <c r="C13" s="1">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1902,16 +1776,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>0.0263146348297596</v>
+        <v>0.02378664165735245</v>
       </c>
       <c r="C14" s="1">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1928,16 +1802,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>0.0263146348297596</v>
+        <v>0.02225201949477196</v>
       </c>
       <c r="C15" s="1">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1954,19 +1828,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>0.0244077779352665</v>
+        <v>0.01918277516961098</v>
       </c>
       <c r="C16" s="1">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F16" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1980,16 +1854,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>0.02364503405988216</v>
+        <v>0.01803180947899818</v>
       </c>
       <c r="C17" s="1">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2006,16 +1880,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>0.02288229204714298</v>
+        <v>0.01803180947899818</v>
       </c>
       <c r="C18" s="1">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2032,16 +1906,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>0.02211954817175865</v>
+        <v>0.01726449839770794</v>
       </c>
       <c r="C19" s="1">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2058,16 +1932,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>0.01906857639551163</v>
+        <v>0.01534622069448233</v>
       </c>
       <c r="C20" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2084,16 +1958,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>0.01792446151375771</v>
+        <v>0.0149625651538372</v>
       </c>
       <c r="C21" s="1">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2110,16 +1984,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>0.01792446151375771</v>
+        <v>0.0149625651538372</v>
       </c>
       <c r="C22" s="1">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2136,16 +2010,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>0.01716171950101852</v>
+        <v>0.01457890961319208</v>
       </c>
       <c r="C23" s="1">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2162,16 +2036,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.01525486074388027</v>
+        <v>0.01419525407254696</v>
       </c>
       <c r="C24" s="1">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2188,16 +2062,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.01487348973751068</v>
+        <v>0.01381159853190184</v>
       </c>
       <c r="C25" s="1">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2214,16 +2088,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>0.01487348973751068</v>
+        <v>0.01342794299125671</v>
       </c>
       <c r="C26" s="1">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2240,16 +2114,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.01487348973751068</v>
+        <v>0.01304428745061159</v>
       </c>
       <c r="C27" s="1">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2266,16 +2140,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0.01449211779981852</v>
+        <v>0.01266063190996647</v>
       </c>
       <c r="C28" s="1">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2292,16 +2166,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>0.01411074679344893</v>
+        <v>0.01189332082867622</v>
       </c>
       <c r="C29" s="1">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2318,16 +2192,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>0.01372937485575676</v>
+        <v>0.009975043125450611</v>
       </c>
       <c r="C30" s="1">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2344,16 +2218,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>0.01334800384938717</v>
+        <v>0.009975043125450611</v>
       </c>
       <c r="C31" s="1">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2370,16 +2244,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>0.012966631911695</v>
+        <v>0.009591387584805489</v>
       </c>
       <c r="C32" s="1">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2396,16 +2270,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>0.01258525997400284</v>
+        <v>0.008440420962870121</v>
       </c>
       <c r="C33" s="1">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2422,16 +2296,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01182251702994108</v>
+        <v>0.008440420962870121</v>
       </c>
       <c r="C34" s="1">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2448,16 +2322,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="2">
-        <v>0.009915660135447979</v>
+        <v>0.006138488184660673</v>
       </c>
       <c r="C35" s="1">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2474,16 +2348,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="2">
-        <v>0.009915660135447979</v>
+        <v>0.005371177103370428</v>
       </c>
       <c r="C36" s="1">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2500,16 +2374,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>0.009534288197755814</v>
+        <v>0.005371177103370428</v>
       </c>
       <c r="C37" s="1">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2526,16 +2400,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>0.009152916260063648</v>
+        <v>0.004987521562725306</v>
       </c>
       <c r="C38" s="1">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2552,16 +2426,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.008390173316001892</v>
+        <v>0.004987521562725306</v>
       </c>
       <c r="C39" s="1">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2578,16 +2452,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.008390173316001892</v>
+        <v>0.004220210481435061</v>
       </c>
       <c r="C40" s="1">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2604,16 +2478,16 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.00686468742787838</v>
+        <v>0.003452899632975459</v>
       </c>
       <c r="C41" s="1">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2630,16 +2504,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.006101944483816624</v>
+        <v>0.003069244092330337</v>
       </c>
       <c r="C42" s="1">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2656,16 +2530,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.005339201539754868</v>
+        <v>0.003069244092330337</v>
       </c>
       <c r="C43" s="1">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2682,16 +2556,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.005339201539754868</v>
+        <v>0.002685588551685214</v>
       </c>
       <c r="C44" s="1">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2708,16 +2582,16 @@
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.00495783006772399</v>
+        <v>0.002685588551685214</v>
       </c>
       <c r="C45" s="1">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -2734,16 +2608,16 @@
         <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.00495783006772399</v>
+        <v>0.002685588551685214</v>
       </c>
       <c r="C46" s="1">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -2760,16 +2634,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.004576458130031824</v>
+        <v>0.002301933011040092</v>
       </c>
       <c r="C47" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -2783,45 +2657,45 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>0.004195086658000946</v>
+        <v>0.002301933011040092</v>
       </c>
       <c r="C48" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="E48" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>0.00343234371393919</v>
+        <v>0.002301933011040092</v>
       </c>
       <c r="C49" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -2835,19 +2709,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>0.003050972241908312</v>
+        <v>0.002301933011040092</v>
       </c>
       <c r="C50" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -2861,19 +2735,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.003050972241908312</v>
+        <v>0.001918277586810291</v>
       </c>
       <c r="C51" s="1">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -2887,19 +2761,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.002669600769877434</v>
+        <v>0.001918277586810291</v>
       </c>
       <c r="C52" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -2913,19 +2787,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.002669600769877434</v>
+        <v>0.001534622046165168</v>
       </c>
       <c r="C53" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -2939,19 +2813,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="B54" s="2">
-        <v>0.002669600769877434</v>
+        <v>0.001534622046165168</v>
       </c>
       <c r="C54" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E54" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -2960,24 +2834,24 @@
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.002669600769877434</v>
+        <v>0.001534622046165168</v>
       </c>
       <c r="C55" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -2991,19 +2865,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.002288229065015912</v>
+        <v>0.001150966505520046</v>
       </c>
       <c r="C56" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3017,45 +2891,45 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>0.002288229065015912</v>
+        <v>0.001150966505520046</v>
       </c>
       <c r="C57" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D57" s="1">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>0.002288229065015912</v>
+        <v>0.001150966505520046</v>
       </c>
       <c r="C58" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3069,19 +2943,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.002288229065015912</v>
+        <v>0.0007673110230825841</v>
       </c>
       <c r="C59" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3095,19 +2969,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.001906857592985034</v>
+        <v>0.0003836555115412921</v>
       </c>
       <c r="C60" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3121,19 +2995,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.001906857592985034</v>
+        <v>0.0003836555115412921</v>
       </c>
       <c r="C61" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3147,19 +3021,19 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.001525486120954156</v>
+        <v>0.0003836555115412921</v>
       </c>
       <c r="C62" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3173,19 +3047,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.001525486120954156</v>
+        <v>0.0003836555115412921</v>
       </c>
       <c r="C63" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D63" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3194,402 +3068,38 @@
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B64" s="2">
-        <v>0.001525486120954156</v>
-      </c>
-      <c r="C64" s="1">
-        <v>8</v>
-      </c>
-      <c r="D64" s="1">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1">
-        <v>8</v>
-      </c>
-      <c r="F64" s="1">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0</v>
-      </c>
-      <c r="H64" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="1" t="s">
+      <c r="A64" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="2">
-        <v>0.001525486120954156</v>
-      </c>
-      <c r="C65" s="1">
-        <v>8</v>
-      </c>
-      <c r="D65" s="1">
-        <v>0</v>
-      </c>
-      <c r="E65" s="1">
-        <v>8</v>
-      </c>
-      <c r="F65" s="1">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0</v>
-      </c>
-      <c r="H65" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" s="2">
-        <v>0.001144114532507956</v>
-      </c>
-      <c r="C66" s="1">
-        <v>6</v>
-      </c>
-      <c r="D66" s="1">
-        <v>0</v>
-      </c>
-      <c r="E66" s="1">
-        <v>6</v>
-      </c>
-      <c r="F66" s="1">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="2">
-        <v>0.001144114532507956</v>
-      </c>
-      <c r="C67" s="1">
-        <v>6</v>
-      </c>
-      <c r="D67" s="1">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1">
-        <v>6</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0</v>
-      </c>
-      <c r="H67" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B68" s="2">
-        <v>0.001144114532507956</v>
-      </c>
-      <c r="C68" s="1">
-        <v>6</v>
-      </c>
-      <c r="D68" s="1">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1">
-        <v>6</v>
-      </c>
-      <c r="F68" s="1">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69" s="2">
-        <v>0.001144114532507956</v>
-      </c>
-      <c r="C69" s="1">
-        <v>6</v>
-      </c>
-      <c r="D69" s="1">
-        <v>0</v>
-      </c>
-      <c r="E69" s="1">
-        <v>6</v>
-      </c>
-      <c r="F69" s="1">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0</v>
-      </c>
-      <c r="H69" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B70" s="2">
-        <v>0.001144114532507956</v>
-      </c>
-      <c r="C70" s="1">
-        <v>6</v>
-      </c>
-      <c r="D70" s="1">
-        <v>0</v>
-      </c>
-      <c r="E70" s="1">
-        <v>6</v>
-      </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0</v>
-      </c>
-      <c r="H70" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71" s="2">
-        <v>0.001144114532507956</v>
-      </c>
-      <c r="C71" s="1">
-        <v>6</v>
-      </c>
-      <c r="D71" s="1">
-        <v>0</v>
-      </c>
-      <c r="E71" s="1">
-        <v>6</v>
-      </c>
-      <c r="F71" s="1">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0</v>
-      </c>
-      <c r="H71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="2">
-        <v>0.000762743060477078</v>
-      </c>
-      <c r="C72" s="1">
-        <v>4</v>
-      </c>
-      <c r="D72" s="1">
-        <v>0</v>
-      </c>
-      <c r="E72" s="1">
-        <v>4</v>
-      </c>
-      <c r="F72" s="1">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0</v>
-      </c>
-      <c r="H72" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B73" s="2">
-        <v>0.000762743060477078</v>
-      </c>
-      <c r="C73" s="1">
-        <v>4</v>
-      </c>
-      <c r="D73" s="1">
-        <v>0</v>
-      </c>
-      <c r="E73" s="1">
-        <v>4</v>
-      </c>
-      <c r="F73" s="1">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0</v>
-      </c>
-      <c r="H73" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B74" s="2">
-        <v>0.000381371530238539</v>
-      </c>
-      <c r="C74" s="1">
-        <v>2</v>
-      </c>
-      <c r="D74" s="1">
-        <v>0</v>
-      </c>
-      <c r="E74" s="1">
-        <v>2</v>
-      </c>
-      <c r="F74" s="1">
-        <v>0</v>
-      </c>
-      <c r="G74" s="1">
-        <v>0</v>
-      </c>
-      <c r="H74" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B75" s="2">
-        <v>0.000381371530238539</v>
-      </c>
-      <c r="C75" s="1">
-        <v>2</v>
-      </c>
-      <c r="D75" s="1">
-        <v>0</v>
-      </c>
-      <c r="E75" s="1">
-        <v>2</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0</v>
-      </c>
-      <c r="H75" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B76" s="2">
-        <v>0.000381371530238539</v>
-      </c>
-      <c r="C76" s="1">
-        <v>2</v>
-      </c>
-      <c r="D76" s="1">
-        <v>0</v>
-      </c>
-      <c r="E76" s="1">
-        <v>2</v>
-      </c>
-      <c r="F76" s="1">
-        <v>0</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0</v>
-      </c>
-      <c r="H76" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B77" s="2">
-        <v>0.000381371530238539</v>
-      </c>
-      <c r="C77" s="1">
-        <v>2</v>
-      </c>
-      <c r="D77" s="1">
-        <v>0</v>
-      </c>
-      <c r="E77" s="1">
-        <v>2</v>
-      </c>
-      <c r="F77" s="1">
-        <v>0</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0</v>
-      </c>
-      <c r="H77" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-      <c r="B78">
+      <c r="B64">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C78">
+      <c r="C64">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D78">
+      <c r="D64">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E78">
+      <c r="E64">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F78">
+      <c r="F64">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G78">
+      <c r="G64">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H78">
+      <c r="H64">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/AT32 FOR LVGL/app/project/MDK_V5/AT32F403AVGT7_WorkBench_analysis.xlsx
+++ b/AT32 FOR LVGL/app/project/MDK_V5/AT32F403AVGT7_WorkBench_analysis.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="81">
   <si>
     <t>AT32F403AVGT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-d426df.o</t>
+    <t>lto-llvm-92863b.o</t>
   </si>
   <si>
     <t>startup_at32f403a_407.o</t>
@@ -53,6 +53,9 @@
     <t>fopen.o</t>
   </si>
   <si>
+    <t>_printf_intcommon.o</t>
+  </si>
+  <si>
     <t>rt_memcpy_v6.o</t>
   </si>
   <si>
@@ -62,9 +65,15 @@
     <t>strcmpv7em.o</t>
   </si>
   <si>
+    <t>_printf_dec.o</t>
+  </si>
+  <si>
     <t>llsdiv.o</t>
   </si>
   <si>
+    <t>__printf.o</t>
+  </si>
+  <si>
     <t>rt_memcpy_w.o</t>
   </si>
   <si>
@@ -74,9 +83,6 @@
     <t>__scatter.o</t>
   </si>
   <si>
-    <t>__dczerorl2.o</t>
-  </si>
-  <si>
     <t>defsig_rtmem_inner.o</t>
   </si>
   <si>
@@ -116,12 +122,18 @@
     <t>defsig_general.o</t>
   </si>
   <si>
+    <t>_printf_char_common.o</t>
+  </si>
+  <si>
     <t>puts.o</t>
   </si>
   <si>
     <t>init_aeabi.o</t>
   </si>
   <si>
+    <t>_printf_char_file.o</t>
+  </si>
+  <si>
     <t>systick_wrapper_gnu.o</t>
   </si>
   <si>
@@ -137,6 +149,12 @@
     <t>fpinit.o</t>
   </si>
   <si>
+    <t>__scatter_copy.o</t>
+  </si>
+  <si>
+    <t>noretval__2printf.o</t>
+  </si>
+  <si>
     <t>libinit2.o</t>
   </si>
   <si>
@@ -176,6 +194,9 @@
     <t>rt_errno_addr_intlibspace.o</t>
   </si>
   <si>
+    <t>ferror.o</t>
+  </si>
+  <si>
     <t>__main.o</t>
   </si>
   <si>
@@ -185,10 +206,16 @@
     <t>heapauxi.o</t>
   </si>
   <si>
+    <t>_printf_u.o</t>
+  </si>
+  <si>
     <t>__rtentry4.o</t>
   </si>
   <si>
     <t>hguard.o</t>
+  </si>
+  <si>
+    <t>_printf_percent_end.o</t>
   </si>
   <si>
     <t>use_no_semi.o</t>
@@ -320,11 +347,11 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$64</c:f>
+              <c:f>ram_percent!$A$3:$A$73</c:f>
               <c:strCache>
-                <c:ptCount val="62"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-d426df.o</c:v>
+                  <c:v>lto-llvm-92863b.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f403a_407.o</c:v>
@@ -338,7 +365,7 @@
                 <c:pt idx="4">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="70">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -346,26 +373,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$64</c:f>
+              <c:f>ram_percent!$B$3:$B$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
-                  <c:v>98.33460998535156</c:v>
+                  <c:v>98.32932281494141</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.133880615234375</c:v>
+                  <c:v>1.137482881546021</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2657532691955566</c:v>
+                  <c:v>0.2665975391864777</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1948857307434082</c:v>
+                  <c:v>0.1955048739910126</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.07086753845214844</c:v>
-                </c:pt>
-                <c:pt idx="61">
+                  <c:v>0.07109268009662628</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -433,11 +460,11 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$64</c:f>
+              <c:f>flash_percent!$A$3:$A$73</c:f>
               <c:strCache>
-                <c:ptCount val="62"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-d426df.o</c:v>
+                  <c:v>lto-llvm-92863b.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>c_w.l</c:v>
@@ -464,162 +491,189 @@
                   <c:v>fopen.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>_printf_intcommon.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>init_alloc.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>strcmpv7em.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>_printf_dec.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>llsdiv.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
+                  <c:v>__printf.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
                   <c:v>h1_alloc.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="18">
                   <c:v>__scatter.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>__dczerorl2.o</c:v>
-                </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>defsig_rtmem_inner.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>h1_free.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>fclose.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>strcpy.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>setvbuf.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>rt_memclr.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>ftell.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="28">
                   <c:v>strlen.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>h1_extend.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>defsig_rtred_inner.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>defsig_general.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
+                  <c:v>_printf_char_common.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>puts.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="34">
                   <c:v>init_aeabi.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="35">
+                  <c:v>_printf_char_file.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>systick_wrapper_gnu.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="37">
                   <c:v>fputc.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="38">
                   <c:v>__scatter_zi.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="39">
                   <c:v>fz_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="40">
                   <c:v>fpinit.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="41">
+                  <c:v>__scatter_copy.o</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>noretval__2printf.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>libinit2.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="44">
                   <c:v>exit.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="45">
                   <c:v>aeabi_memset4.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="46">
                   <c:v>aeabi_memset.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="47">
                   <c:v>sys_wrch.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="48">
                   <c:v>defsig_rtred_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="49">
                   <c:v>defsig_rtmem_outer.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="50">
                   <c:v>sys_exit.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="51">
                   <c:v>stdio_streams.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="52">
                   <c:v>h1_init.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="53">
                   <c:v>__rtentry2.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="54">
                   <c:v>rtexit2.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="55">
                   <c:v>defsig_exit.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="56">
                   <c:v>rt_errno_addr_intlibspace.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="57">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="58">
+                  <c:v>ferror.o</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>__main.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="60">
                   <c:v>libshutdown2.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="61">
                   <c:v>heapauxi.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="62">
+                  <c:v>_printf_u.o</c:v>
+                </c:pt>
+                <c:pt idx="63">
                   <c:v>__rtentry4.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="64">
                   <c:v>hguard.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="65">
+                  <c:v>_printf_percent_end.o</c:v>
+                </c:pt>
+                <c:pt idx="66">
                   <c:v>use_no_semi.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="67">
                   <c:v>rtexit.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="68">
                   <c:v>libshutdown.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="69">
                   <c:v>libinit.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="70">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -627,194 +681,221 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$64</c:f>
+              <c:f>flash_percent!$B$3:$B$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
-                  <c:v>98.38481140136719</c:v>
+                  <c:v>97.50539398193359</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7569523453712463</c:v>
+                  <c:v>1.176853656768799</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.09246097505092621</c:v>
+                  <c:v>0.1286266297101975</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.08670614659786224</c:v>
+                  <c:v>0.1206208243966103</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.05985026061534882</c:v>
+                  <c:v>0.08326039463281632</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.05064252763986588</c:v>
+                  <c:v>0.07045110315084457</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0475732833147049</c:v>
+                  <c:v>0.06618133932352066</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.04603866115212441</c:v>
+                  <c:v>0.0640464574098587</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.04603866115212441</c:v>
+                  <c:v>0.0640464574098587</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.02647222951054573</c:v>
+                  <c:v>0.04750112071633339</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.02647222951054573</c:v>
+                  <c:v>0.03682671114802361</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.02378664165735245</c:v>
+                  <c:v>0.03682671114802361</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.02225201949477196</c:v>
+                  <c:v>0.03309066966176033</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01918277516961098</c:v>
+                  <c:v>0.03202322870492935</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01803180947899818</c:v>
+                  <c:v>0.03095578588545322</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01803180947899818</c:v>
+                  <c:v>0.02775346301496029</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.01726449839770794</c:v>
+                  <c:v>0.02668602205812931</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.01534622069448233</c:v>
+                  <c:v>0.02508486062288284</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.0149625651538372</c:v>
+                  <c:v>0.02508486062288284</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.0149625651538372</c:v>
+                  <c:v>0.02134881913661957</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.01457890961319208</c:v>
+                  <c:v>0.02081509865820408</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.01419525407254696</c:v>
+                  <c:v>0.02081509865820408</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.01381159853190184</c:v>
+                  <c:v>0.02028137817978859</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.01342794299125671</c:v>
+                  <c:v>0.0197476577013731</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.01304428745061159</c:v>
+                  <c:v>0.01921393722295761</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.01266063190996647</c:v>
+                  <c:v>0.01868021674454212</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.01189332082867622</c:v>
+                  <c:v>0.01814649626612663</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.009975043125450611</c:v>
+                  <c:v>0.01761277578771114</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.009975043125450611</c:v>
+                  <c:v>0.01654533483088017</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.009591387584805489</c:v>
+                  <c:v>0.01387673150748015</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.008440420962870121</c:v>
+                  <c:v>0.01387673150748015</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.008440420962870121</c:v>
+                  <c:v>0.01334301102906466</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.006138488184660673</c:v>
+                  <c:v>0.01280929055064917</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.005371177103370428</c:v>
+                  <c:v>0.01174185052514076</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.005371177103370428</c:v>
+                  <c:v>0.01174185052514076</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.004987521562725306</c:v>
+                  <c:v>0.009606968611478806</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.004987521562725306</c:v>
+                  <c:v>0.008539527654647827</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.004220210481435061</c:v>
+                  <c:v>0.007472086232155561</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.003452899632975459</c:v>
+                  <c:v>0.007472086232155561</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.003069244092330337</c:v>
+                  <c:v>0.006938365753740072</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.003069244092330337</c:v>
+                  <c:v>0.006938365753740072</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.002685588551685214</c:v>
+                  <c:v>0.006938365753740072</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.002685588551685214</c:v>
+                  <c:v>0.006404645275324583</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.002685588551685214</c:v>
+                  <c:v>0.005870925262570381</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.002301933011040092</c:v>
+                  <c:v>0.004803484305739403</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.002301933011040092</c:v>
+                  <c:v>0.004269763827323914</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.002301933011040092</c:v>
+                  <c:v>0.004269763827323914</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.002301933011040092</c:v>
+                  <c:v>0.003736043116077781</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.001918277586810291</c:v>
+                  <c:v>0.003736043116077781</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.001918277586810291</c:v>
+                  <c:v>0.003736043116077781</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.001534622046165168</c:v>
+                  <c:v>0.003202322637662292</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.001534622046165168</c:v>
+                  <c:v>0.003202322637662292</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.001534622046165168</c:v>
+                  <c:v>0.003202322637662292</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.001150966505520046</c:v>
+                  <c:v>0.003202322637662292</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.001150966505520046</c:v>
+                  <c:v>0.002668602392077446</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.001150966505520046</c:v>
+                  <c:v>0.002668602392077446</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.0007673110230825841</c:v>
+                  <c:v>0.002134881913661957</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.0003836555115412921</c:v>
+                  <c:v>0.002134881913661957</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.0003836555115412921</c:v>
+                  <c:v>0.002134881913661957</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.0003836555115412921</c:v>
+                  <c:v>0.002134881913661957</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.0003836555115412921</c:v>
+                  <c:v>0.001601161318831146</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>0.001601161318831146</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.001601161318831146</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.001601161318831146</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.001067440956830978</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.001067440956830978</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.0005337204784154892</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.0005337204784154892</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.0005337204784154892</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.0005337204784154892</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -919,8 +1000,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H64" totalsRowCount="1">
-  <autoFilter ref="A2:H63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H73" totalsRowCount="1">
+  <autoFilter ref="A2:H72"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -936,8 +1017,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H64" totalsRowCount="1">
-  <autoFilter ref="A2:H63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H73" totalsRowCount="1">
+  <autoFilter ref="A2:H72"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1237,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1250,28 +1331,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1279,25 +1360,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>98.33460998535156</v>
+        <v>98.32932281494141</v>
       </c>
       <c r="C3" s="1">
-        <v>133208</v>
+        <v>132779</v>
       </c>
       <c r="D3" s="1">
-        <v>512881</v>
+        <v>365380</v>
       </c>
       <c r="E3" s="1">
-        <v>380766</v>
+        <v>347578</v>
       </c>
       <c r="F3" s="1">
-        <v>131727</v>
+        <v>17744</v>
       </c>
       <c r="G3" s="1">
-        <v>388</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1">
-        <v>132820</v>
+        <v>132721</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1305,7 +1386,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>1.133880615234375</v>
+        <v>1.137482881546021</v>
       </c>
       <c r="C4" s="1">
         <v>1536</v>
@@ -1331,16 +1412,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>0.2657532691955566</v>
+        <v>0.2665975391864777</v>
       </c>
       <c r="C5" s="1">
         <v>360</v>
       </c>
       <c r="D5" s="1">
-        <v>3946</v>
+        <v>4410</v>
       </c>
       <c r="E5" s="1">
-        <v>3934</v>
+        <v>4398</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1357,7 +1438,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.1948857307434082</v>
+        <v>0.1955048739910126</v>
       </c>
       <c r="C6" s="1">
         <v>264</v>
@@ -1383,7 +1464,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.07086753845214844</v>
+        <v>0.07109268009662628</v>
       </c>
       <c r="C7" s="1">
         <v>96</v>
@@ -1404,35 +1485,35 @@
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
-      <c r="A64" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64">
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C64">
+      <c r="C73">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D64">
+      <c r="D73">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E64">
+      <c r="E73">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F64">
+      <c r="F73">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G64">
+      <c r="G73">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H64">
+      <c r="H73">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1448,7 +1529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1461,28 +1542,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1490,25 +1571,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>98.38481140136719</v>
+        <v>97.50539398193359</v>
       </c>
       <c r="C3" s="1">
-        <v>512881</v>
+        <v>365380</v>
       </c>
       <c r="D3" s="1">
-        <v>133208</v>
+        <v>132779</v>
       </c>
       <c r="E3" s="1">
-        <v>380766</v>
+        <v>347578</v>
       </c>
       <c r="F3" s="1">
-        <v>131727</v>
+        <v>17744</v>
       </c>
       <c r="G3" s="1">
-        <v>388</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1">
-        <v>132820</v>
+        <v>132721</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1516,16 +1597,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>0.7569523453712463</v>
+        <v>1.176853656768799</v>
       </c>
       <c r="C4" s="1">
-        <v>3946</v>
+        <v>4410</v>
       </c>
       <c r="D4" s="1">
         <v>360</v>
       </c>
       <c r="E4" s="1">
-        <v>3934</v>
+        <v>4398</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1542,7 +1623,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>0.09246097505092621</v>
+        <v>0.1286266297101975</v>
       </c>
       <c r="C5" s="1">
         <v>482</v>
@@ -1568,7 +1649,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>0.08670614659786224</v>
+        <v>0.1206208243966103</v>
       </c>
       <c r="C6" s="1">
         <v>452</v>
@@ -1594,7 +1675,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>0.05985026061534882</v>
+        <v>0.08326039463281632</v>
       </c>
       <c r="C7" s="1">
         <v>312</v>
@@ -1620,7 +1701,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.05064252763986588</v>
+        <v>0.07045110315084457</v>
       </c>
       <c r="C8" s="1">
         <v>264</v>
@@ -1646,7 +1727,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>0.0475732833147049</v>
+        <v>0.06618133932352066</v>
       </c>
       <c r="C9" s="1">
         <v>248</v>
@@ -1672,7 +1753,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>0.04603866115212441</v>
+        <v>0.0640464574098587</v>
       </c>
       <c r="C10" s="1">
         <v>240</v>
@@ -1698,7 +1779,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>0.04603866115212441</v>
+        <v>0.0640464574098587</v>
       </c>
       <c r="C11" s="1">
         <v>240</v>
@@ -1724,16 +1805,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>0.02647222951054573</v>
+        <v>0.04750112071633339</v>
       </c>
       <c r="C12" s="1">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1750,7 +1831,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>0.02647222951054573</v>
+        <v>0.03682671114802361</v>
       </c>
       <c r="C13" s="1">
         <v>138</v>
@@ -1776,16 +1857,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>0.02378664165735245</v>
+        <v>0.03682671114802361</v>
       </c>
       <c r="C14" s="1">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1802,16 +1883,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>0.02225201949477196</v>
+        <v>0.03309066966176033</v>
       </c>
       <c r="C15" s="1">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1828,16 +1909,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01918277516961098</v>
+        <v>0.03202322870492935</v>
       </c>
       <c r="C16" s="1">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1854,16 +1935,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01803180947899818</v>
+        <v>0.03095578588545322</v>
       </c>
       <c r="C17" s="1">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1880,16 +1961,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01803180947899818</v>
+        <v>0.02775346301496029</v>
       </c>
       <c r="C18" s="1">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1906,16 +1987,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>0.01726449839770794</v>
+        <v>0.02668602205812931</v>
       </c>
       <c r="C19" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1932,16 +2013,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>0.01534622069448233</v>
+        <v>0.02508486062288284</v>
       </c>
       <c r="C20" s="1">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1958,16 +2039,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>0.0149625651538372</v>
+        <v>0.02508486062288284</v>
       </c>
       <c r="C21" s="1">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1984,16 +2065,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>0.0149625651538372</v>
+        <v>0.02134881913661957</v>
       </c>
       <c r="C22" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2010,16 +2091,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>0.01457890961319208</v>
+        <v>0.02081509865820408</v>
       </c>
       <c r="C23" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2036,16 +2117,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.01419525407254696</v>
+        <v>0.02081509865820408</v>
       </c>
       <c r="C24" s="1">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2062,16 +2143,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.01381159853190184</v>
+        <v>0.02028137817978859</v>
       </c>
       <c r="C25" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2088,16 +2169,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>0.01342794299125671</v>
+        <v>0.0197476577013731</v>
       </c>
       <c r="C26" s="1">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2114,16 +2195,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.01304428745061159</v>
+        <v>0.01921393722295761</v>
       </c>
       <c r="C27" s="1">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2140,16 +2221,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0.01266063190996647</v>
+        <v>0.01868021674454212</v>
       </c>
       <c r="C28" s="1">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2166,16 +2247,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>0.01189332082867622</v>
+        <v>0.01814649626612663</v>
       </c>
       <c r="C29" s="1">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2192,16 +2273,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>0.009975043125450611</v>
+        <v>0.01761277578771114</v>
       </c>
       <c r="C30" s="1">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2218,16 +2299,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>0.009975043125450611</v>
+        <v>0.01654533483088017</v>
       </c>
       <c r="C31" s="1">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2244,16 +2325,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>0.009591387584805489</v>
+        <v>0.01387673150748015</v>
       </c>
       <c r="C32" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2270,16 +2351,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>0.008440420962870121</v>
+        <v>0.01387673150748015</v>
       </c>
       <c r="C33" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2296,16 +2377,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>0.008440420962870121</v>
+        <v>0.01334301102906466</v>
       </c>
       <c r="C34" s="1">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2322,16 +2403,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="2">
-        <v>0.006138488184660673</v>
+        <v>0.01280929055064917</v>
       </c>
       <c r="C35" s="1">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2348,16 +2429,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="2">
-        <v>0.005371177103370428</v>
+        <v>0.01174185052514076</v>
       </c>
       <c r="C36" s="1">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2374,16 +2455,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>0.005371177103370428</v>
+        <v>0.01174185052514076</v>
       </c>
       <c r="C37" s="1">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2400,16 +2481,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>0.004987521562725306</v>
+        <v>0.009606968611478806</v>
       </c>
       <c r="C38" s="1">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2426,16 +2507,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.004987521562725306</v>
+        <v>0.008539527654647827</v>
       </c>
       <c r="C39" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2452,16 +2533,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.004220210481435061</v>
+        <v>0.007472086232155561</v>
       </c>
       <c r="C40" s="1">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2478,16 +2559,16 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.003452899632975459</v>
+        <v>0.007472086232155561</v>
       </c>
       <c r="C41" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2504,16 +2585,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.003069244092330337</v>
+        <v>0.006938365753740072</v>
       </c>
       <c r="C42" s="1">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2530,16 +2611,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.003069244092330337</v>
+        <v>0.006938365753740072</v>
       </c>
       <c r="C43" s="1">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2556,16 +2637,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.002685588551685214</v>
+        <v>0.006938365753740072</v>
       </c>
       <c r="C44" s="1">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2582,16 +2663,16 @@
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.002685588551685214</v>
+        <v>0.006404645275324583</v>
       </c>
       <c r="C45" s="1">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -2608,16 +2689,16 @@
         <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.002685588551685214</v>
+        <v>0.005870925262570381</v>
       </c>
       <c r="C46" s="1">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -2634,16 +2715,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.002301933011040092</v>
+        <v>0.004803484305739403</v>
       </c>
       <c r="C47" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -2657,45 +2738,45 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B48" s="2">
-        <v>0.002301933011040092</v>
+        <v>0.004269763827323914</v>
       </c>
       <c r="C48" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D48" s="1">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.002301933011040092</v>
+        <v>0.004269763827323914</v>
       </c>
       <c r="C49" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -2709,19 +2790,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.002301933011040092</v>
+        <v>0.003736043116077781</v>
       </c>
       <c r="C50" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -2735,19 +2816,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.001918277586810291</v>
+        <v>0.003736043116077781</v>
       </c>
       <c r="C51" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -2761,19 +2842,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>0.001918277586810291</v>
+        <v>0.003736043116077781</v>
       </c>
       <c r="C52" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -2787,19 +2868,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>0.001534622046165168</v>
+        <v>0.003202322637662292</v>
       </c>
       <c r="C53" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -2813,45 +2894,45 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>0.001534622046165168</v>
+        <v>0.003202322637662292</v>
       </c>
       <c r="C54" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D54" s="1">
-        <v>96</v>
+        <v>264</v>
       </c>
       <c r="E54" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H54" s="1">
-        <v>96</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.001534622046165168</v>
+        <v>0.003202322637662292</v>
       </c>
       <c r="C55" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -2865,19 +2946,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.001150966505520046</v>
+        <v>0.003202322637662292</v>
       </c>
       <c r="C56" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -2891,19 +2972,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.001150966505520046</v>
+        <v>0.002668602392077446</v>
       </c>
       <c r="C57" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -2917,19 +2998,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2">
-        <v>0.001150966505520046</v>
+        <v>0.002668602392077446</v>
       </c>
       <c r="C58" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -2943,19 +3024,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2">
-        <v>0.0007673110230825841</v>
+        <v>0.002134881913661957</v>
       </c>
       <c r="C59" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -2969,19 +3050,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="B60" s="2">
-        <v>0.0003836555115412921</v>
+        <v>0.002134881913661957</v>
       </c>
       <c r="C60" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E60" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -2990,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2998,16 +3079,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.0003836555115412921</v>
+        <v>0.002134881913661957</v>
       </c>
       <c r="C61" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3024,16 +3105,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.0003836555115412921</v>
+        <v>0.002134881913661957</v>
       </c>
       <c r="C62" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3050,56 +3131,290 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.0003836555115412921</v>
+        <v>0.001601161318831146</v>
       </c>
       <c r="C63" s="1">
+        <v>6</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>6</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0.001601161318831146</v>
+      </c>
+      <c r="C64" s="1">
+        <v>6</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
+        <v>6</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2">
+        <v>0.001601161318831146</v>
+      </c>
+      <c r="C65" s="1">
+        <v>6</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1">
+        <v>6</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.001601161318831146</v>
+      </c>
+      <c r="C66" s="1">
+        <v>6</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>6</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.001067440956830978</v>
+      </c>
+      <c r="C67" s="1">
+        <v>4</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
+        <v>4</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.001067440956830978</v>
+      </c>
+      <c r="C68" s="1">
+        <v>4</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
+        <v>4</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.0005337204784154892</v>
+      </c>
+      <c r="C69" s="1">
         <v>2</v>
       </c>
-      <c r="D63" s="1">
-        <v>0</v>
-      </c>
-      <c r="E63" s="1">
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="1">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0</v>
-      </c>
-      <c r="H63" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64">
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.0005337204784154892</v>
+      </c>
+      <c r="C70" s="1">
+        <v>2</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
+        <v>2</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.0005337204784154892</v>
+      </c>
+      <c r="C71" s="1">
+        <v>2</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.0005337204784154892</v>
+      </c>
+      <c r="C72" s="1">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>2</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C64">
+      <c r="C73">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D64">
+      <c r="D73">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E64">
+      <c r="E73">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F64">
+      <c r="F73">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G64">
+      <c r="G73">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H64">
+      <c r="H73">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/AT32 FOR LVGL/app/project/MDK_V5/AT32F403AVGT7_WorkBench_analysis.xlsx
+++ b/AT32 FOR LVGL/app/project/MDK_V5/AT32F403AVGT7_WorkBench_analysis.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
   <si>
     <t>AT32F403AVGT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-92863b.o</t>
+    <t>lto-llvm-b5a238.o</t>
   </si>
   <si>
     <t>startup_at32f403a_407.o</t>
@@ -53,9 +53,6 @@
     <t>fopen.o</t>
   </si>
   <si>
-    <t>_printf_intcommon.o</t>
-  </si>
-  <si>
     <t>rt_memcpy_v6.o</t>
   </si>
   <si>
@@ -65,15 +62,9 @@
     <t>strcmpv7em.o</t>
   </si>
   <si>
-    <t>_printf_dec.o</t>
-  </si>
-  <si>
     <t>llsdiv.o</t>
   </si>
   <si>
-    <t>__printf.o</t>
-  </si>
-  <si>
     <t>rt_memcpy_w.o</t>
   </si>
   <si>
@@ -122,18 +113,12 @@
     <t>defsig_general.o</t>
   </si>
   <si>
-    <t>_printf_char_common.o</t>
-  </si>
-  <si>
     <t>puts.o</t>
   </si>
   <si>
     <t>init_aeabi.o</t>
   </si>
   <si>
-    <t>_printf_char_file.o</t>
-  </si>
-  <si>
     <t>systick_wrapper_gnu.o</t>
   </si>
   <si>
@@ -152,9 +137,6 @@
     <t>__scatter_copy.o</t>
   </si>
   <si>
-    <t>noretval__2printf.o</t>
-  </si>
-  <si>
     <t>libinit2.o</t>
   </si>
   <si>
@@ -194,9 +176,6 @@
     <t>rt_errno_addr_intlibspace.o</t>
   </si>
   <si>
-    <t>ferror.o</t>
-  </si>
-  <si>
     <t>__main.o</t>
   </si>
   <si>
@@ -206,16 +185,10 @@
     <t>heapauxi.o</t>
   </si>
   <si>
-    <t>_printf_u.o</t>
-  </si>
-  <si>
     <t>__rtentry4.o</t>
   </si>
   <si>
     <t>hguard.o</t>
-  </si>
-  <si>
-    <t>_printf_percent_end.o</t>
   </si>
   <si>
     <t>use_no_semi.o</t>
@@ -347,11 +320,11 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$73</c:f>
+              <c:f>ram_percent!$A$3:$A$64</c:f>
               <c:strCache>
-                <c:ptCount val="71"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-92863b.o</c:v>
+                  <c:v>lto-llvm-b5a238.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f403a_407.o</c:v>
@@ -365,7 +338,7 @@
                 <c:pt idx="4">
                   <c:v>libspace.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="61">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -373,26 +346,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$73</c:f>
+              <c:f>ram_percent!$B$3:$B$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>98.32932281494141</c:v>
+                  <c:v>98.3292236328125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.137482881546021</c:v>
+                  <c:v>1.137550234794617</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2665975391864777</c:v>
+                  <c:v>0.2666133344173431</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1955048739910126</c:v>
+                  <c:v>0.1955164521932602</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.07109268009662628</c:v>
-                </c:pt>
-                <c:pt idx="70">
+                  <c:v>0.07109688967466354</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -460,11 +433,11 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$73</c:f>
+              <c:f>flash_percent!$A$3:$A$64</c:f>
               <c:strCache>
-                <c:ptCount val="71"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-92863b.o</c:v>
+                  <c:v>lto-llvm-b5a238.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>c_w.l</c:v>
@@ -491,189 +464,162 @@
                   <c:v>fopen.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>_printf_intcommon.o</c:v>
+                  <c:v>rt_memcpy_v6.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>rt_memcpy_v6.o</c:v>
+                  <c:v>init_alloc.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>init_alloc.o</c:v>
+                  <c:v>strcmpv7em.o</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>strcmpv7em.o</c:v>
+                  <c:v>llsdiv.o</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>_printf_dec.o</c:v>
+                  <c:v>rt_memcpy_w.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>llsdiv.o</c:v>
+                  <c:v>h1_alloc.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>__printf.o</c:v>
+                  <c:v>__scatter.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>rt_memcpy_w.o</c:v>
+                  <c:v>defsig_rtmem_inner.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>h1_alloc.o</c:v>
+                  <c:v>rt_memclr_w.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>__scatter.o</c:v>
+                  <c:v>h1_free.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>defsig_rtmem_inner.o</c:v>
+                  <c:v>fclose.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>rt_memclr_w.o</c:v>
+                  <c:v>sys_stackheap_outer.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>h1_free.o</c:v>
+                  <c:v>strcpy.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>fclose.o</c:v>
+                  <c:v>setvbuf.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>sys_stackheap_outer.o</c:v>
+                  <c:v>rt_memclr.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>strcpy.o</c:v>
+                  <c:v>ftell.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>setvbuf.o</c:v>
+                  <c:v>strlen.o</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>rt_memclr.o</c:v>
+                  <c:v>h1_extend.o</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>ftell.o</c:v>
+                  <c:v>defsig_rtred_inner.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>strlen.o</c:v>
+                  <c:v>defsig_general.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>h1_extend.o</c:v>
+                  <c:v>puts.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>defsig_rtred_inner.o</c:v>
+                  <c:v>init_aeabi.o</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>defsig_general.o</c:v>
+                  <c:v>systick_wrapper_gnu.o</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>_printf_char_common.o</c:v>
+                  <c:v>fputc.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>puts.o</c:v>
+                  <c:v>__scatter_zi.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>init_aeabi.o</c:v>
+                  <c:v>fz_wm.l</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>_printf_char_file.o</c:v>
+                  <c:v>fpinit.o</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>systick_wrapper_gnu.o</c:v>
+                  <c:v>__scatter_copy.o</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>fputc.o</c:v>
+                  <c:v>libinit2.o</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>__scatter_zi.o</c:v>
+                  <c:v>exit.o</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>fz_wm.l</c:v>
+                  <c:v>aeabi_memset4.o</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>fpinit.o</c:v>
+                  <c:v>aeabi_memset.o</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>__scatter_copy.o</c:v>
+                  <c:v>sys_wrch.o</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>noretval__2printf.o</c:v>
+                  <c:v>defsig_rtred_outer.o</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>libinit2.o</c:v>
+                  <c:v>defsig_rtmem_outer.o</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>exit.o</c:v>
+                  <c:v>sys_exit.o</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>aeabi_memset4.o</c:v>
+                  <c:v>stdio_streams.o</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>aeabi_memset.o</c:v>
+                  <c:v>h1_init.o</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>sys_wrch.o</c:v>
+                  <c:v>__rtentry2.o</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>defsig_rtred_outer.o</c:v>
+                  <c:v>rtexit2.o</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>defsig_rtmem_outer.o</c:v>
+                  <c:v>defsig_exit.o</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>sys_exit.o</c:v>
+                  <c:v>rt_errno_addr_intlibspace.o</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>stdio_streams.o</c:v>
+                  <c:v>libspace.o</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>h1_init.o</c:v>
+                  <c:v>__main.o</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>__rtentry2.o</c:v>
+                  <c:v>libshutdown2.o</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>rtexit2.o</c:v>
+                  <c:v>heapauxi.o</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>defsig_exit.o</c:v>
+                  <c:v>__rtentry4.o</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>rt_errno_addr_intlibspace.o</c:v>
+                  <c:v>hguard.o</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>libspace.o</c:v>
+                  <c:v>use_no_semi.o</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>ferror.o</c:v>
+                  <c:v>rtexit.o</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>__main.o</c:v>
+                  <c:v>libshutdown.o</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>libshutdown2.o</c:v>
+                  <c:v>libinit.o</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>heapauxi.o</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>_printf_u.o</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>__rtentry4.o</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>hguard.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>_printf_percent_end.o</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>use_no_semi.o</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>rtexit.o</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>libshutdown.o</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>libinit.o</c:v>
-                </c:pt>
-                <c:pt idx="70">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -681,221 +627,194 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$73</c:f>
+              <c:f>flash_percent!$B$3:$B$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="71"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>97.50539398193359</c:v>
+                  <c:v>97.78083801269531</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.176853656768799</c:v>
+                  <c:v>1.038926243782044</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1286266297101975</c:v>
+                  <c:v>0.1289959996938705</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1206208243966103</c:v>
+                  <c:v>0.1209672018885613</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.08326039463281632</c:v>
+                  <c:v>0.0834994837641716</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.07045110315084457</c:v>
+                  <c:v>0.07065340876579285</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.06618133932352066</c:v>
+                  <c:v>0.06637138873338699</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0640464574098587</c:v>
+                  <c:v>0.06423037499189377</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0640464574098587</c:v>
+                  <c:v>0.06423037499189377</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.04750112071633339</c:v>
+                  <c:v>0.03693246468901634</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.03682671114802361</c:v>
+                  <c:v>0.03693246468901634</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.03682671114802361</c:v>
+                  <c:v>0.0331856943666935</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.03309066966176033</c:v>
+                  <c:v>0.03104468062520027</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.03202322870492935</c:v>
+                  <c:v>0.02676265500485897</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.03095578588545322</c:v>
+                  <c:v>0.0251568965613842</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.02775346301496029</c:v>
+                  <c:v>0.0251568965613842</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.02668602205812931</c:v>
+                  <c:v>0.02141012437641621</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.02508486062288284</c:v>
+                  <c:v>0.0208748709410429</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.02508486062288284</c:v>
+                  <c:v>0.0208748709410429</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.02134881913661957</c:v>
+                  <c:v>0.02033961750566959</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.02081509865820408</c:v>
+                  <c:v>0.01980436407029629</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.02081509865820408</c:v>
+                  <c:v>0.01926911249756813</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02028137817978859</c:v>
+                  <c:v>0.01873385906219482</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.0197476577013731</c:v>
+                  <c:v>0.01819860562682152</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.01921393722295761</c:v>
+                  <c:v>0.01766335219144821</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.01868021674454212</c:v>
+                  <c:v>0.01659284718334675</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.01814649626612663</c:v>
+                  <c:v>0.01391658093780279</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.01761277578771114</c:v>
+                  <c:v>0.01391658093780279</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.01654533483088017</c:v>
+                  <c:v>0.01338132750242949</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.01387673150748015</c:v>
+                  <c:v>0.01177556812763214</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.01387673150748015</c:v>
+                  <c:v>0.01177556812763214</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01334301102906466</c:v>
+                  <c:v>0.008564049378037453</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.01280929055064917</c:v>
+                  <c:v>0.007493543438613415</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.01174185052514076</c:v>
+                  <c:v>0.007493543438613415</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.01174185052514076</c:v>
+                  <c:v>0.006958290468901396</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.009606968611478806</c:v>
+                  <c:v>0.006958290468901396</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.008539527654647827</c:v>
+                  <c:v>0.006958290468901396</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.007472086232155561</c:v>
+                  <c:v>0.005887784063816071</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.007472086232155561</c:v>
+                  <c:v>0.004817278124392033</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.006938365753740072</c:v>
+                  <c:v>0.004282024689018726</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.006938365753740072</c:v>
+                  <c:v>0.004282024689018726</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.006938365753740072</c:v>
+                  <c:v>0.003746771719306707</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.006404645275324583</c:v>
+                  <c:v>0.003746771719306707</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.005870925262570381</c:v>
+                  <c:v>0.003746771719306707</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.004803484305739403</c:v>
+                  <c:v>0.003211518749594688</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.004269763827323914</c:v>
+                  <c:v>0.003211518749594688</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.004269763827323914</c:v>
+                  <c:v>0.003211518749594688</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.003736043116077781</c:v>
+                  <c:v>0.003211518749594688</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.003736043116077781</c:v>
+                  <c:v>0.002676265547052026</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.003736043116077781</c:v>
+                  <c:v>0.002676265547052026</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.003202322637662292</c:v>
+                  <c:v>0.002141012344509363</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.003202322637662292</c:v>
+                  <c:v>0.002141012344509363</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.003202322637662292</c:v>
+                  <c:v>0.002141012344509363</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.003202322637662292</c:v>
+                  <c:v>0.001605759374797344</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.002668602392077446</c:v>
+                  <c:v>0.001605759374797344</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.002668602392077446</c:v>
+                  <c:v>0.001605759374797344</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.002134881913661957</c:v>
+                  <c:v>0.001070506172254682</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.002134881913661957</c:v>
+                  <c:v>0.0005352530861273408</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.002134881913661957</c:v>
+                  <c:v>0.0005352530861273408</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.002134881913661957</c:v>
+                  <c:v>0.0005352530861273408</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.001601161318831146</c:v>
+                  <c:v>0.0005352530861273408</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.001601161318831146</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.001601161318831146</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.001601161318831146</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.001067440956830978</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.001067440956830978</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.0005337204784154892</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.0005337204784154892</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.0005337204784154892</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.0005337204784154892</c:v>
-                </c:pt>
-                <c:pt idx="70">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1000,8 +919,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H73" totalsRowCount="1">
-  <autoFilter ref="A2:H72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H64" totalsRowCount="1">
+  <autoFilter ref="A2:H63"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1017,8 +936,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H73" totalsRowCount="1">
-  <autoFilter ref="A2:H72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H64" totalsRowCount="1">
+  <autoFilter ref="A2:H63"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1318,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1331,28 +1250,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1360,22 +1279,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>98.32932281494141</v>
+        <v>98.3292236328125</v>
       </c>
       <c r="C3" s="1">
-        <v>132779</v>
+        <v>132771</v>
       </c>
       <c r="D3" s="1">
-        <v>365380</v>
+        <v>365363</v>
       </c>
       <c r="E3" s="1">
-        <v>347578</v>
+        <v>347640</v>
       </c>
       <c r="F3" s="1">
-        <v>17744</v>
+        <v>17673</v>
       </c>
       <c r="G3" s="1">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H3" s="1">
         <v>132721</v>
@@ -1386,7 +1305,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>1.137482881546021</v>
+        <v>1.137550234794617</v>
       </c>
       <c r="C4" s="1">
         <v>1536</v>
@@ -1412,16 +1331,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>0.2665975391864777</v>
+        <v>0.2666133344173431</v>
       </c>
       <c r="C5" s="1">
         <v>360</v>
       </c>
       <c r="D5" s="1">
-        <v>4410</v>
+        <v>3882</v>
       </c>
       <c r="E5" s="1">
-        <v>4398</v>
+        <v>3870</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1438,7 +1357,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.1955048739910126</v>
+        <v>0.1955164521932602</v>
       </c>
       <c r="C6" s="1">
         <v>264</v>
@@ -1464,7 +1383,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.07109268009662628</v>
+        <v>0.07109688967466354</v>
       </c>
       <c r="C7" s="1">
         <v>96</v>
@@ -1485,35 +1404,35 @@
         <v>96</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
-      <c r="A73" t="s">
-        <v>72</v>
-      </c>
-      <c r="B73">
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C73">
+      <c r="C64">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D73">
+      <c r="D64">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E73">
+      <c r="E64">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F73">
+      <c r="F64">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G73">
+      <c r="G64">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H73">
+      <c r="H64">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1529,7 +1448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1542,28 +1461,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
         <v>71</v>
       </c>
-      <c r="B2" t="s">
-        <v>80</v>
-      </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1571,22 +1490,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>97.50539398193359</v>
+        <v>97.78083801269531</v>
       </c>
       <c r="C3" s="1">
-        <v>365380</v>
+        <v>365363</v>
       </c>
       <c r="D3" s="1">
-        <v>132779</v>
+        <v>132771</v>
       </c>
       <c r="E3" s="1">
-        <v>347578</v>
+        <v>347640</v>
       </c>
       <c r="F3" s="1">
-        <v>17744</v>
+        <v>17673</v>
       </c>
       <c r="G3" s="1">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H3" s="1">
         <v>132721</v>
@@ -1597,16 +1516,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.176853656768799</v>
+        <v>1.038926243782044</v>
       </c>
       <c r="C4" s="1">
-        <v>4410</v>
+        <v>3882</v>
       </c>
       <c r="D4" s="1">
         <v>360</v>
       </c>
       <c r="E4" s="1">
-        <v>4398</v>
+        <v>3870</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1623,7 +1542,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>0.1286266297101975</v>
+        <v>0.1289959996938705</v>
       </c>
       <c r="C5" s="1">
         <v>482</v>
@@ -1649,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>0.1206208243966103</v>
+        <v>0.1209672018885613</v>
       </c>
       <c r="C6" s="1">
         <v>452</v>
@@ -1675,7 +1594,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>0.08326039463281632</v>
+        <v>0.0834994837641716</v>
       </c>
       <c r="C7" s="1">
         <v>312</v>
@@ -1701,7 +1620,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.07045110315084457</v>
+        <v>0.07065340876579285</v>
       </c>
       <c r="C8" s="1">
         <v>264</v>
@@ -1727,7 +1646,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>0.06618133932352066</v>
+        <v>0.06637138873338699</v>
       </c>
       <c r="C9" s="1">
         <v>248</v>
@@ -1753,7 +1672,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>0.0640464574098587</v>
+        <v>0.06423037499189377</v>
       </c>
       <c r="C10" s="1">
         <v>240</v>
@@ -1779,7 +1698,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>0.0640464574098587</v>
+        <v>0.06423037499189377</v>
       </c>
       <c r="C11" s="1">
         <v>240</v>
@@ -1805,16 +1724,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>0.04750112071633339</v>
+        <v>0.03693246468901634</v>
       </c>
       <c r="C12" s="1">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1831,7 +1750,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>0.03682671114802361</v>
+        <v>0.03693246468901634</v>
       </c>
       <c r="C13" s="1">
         <v>138</v>
@@ -1857,16 +1776,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>0.03682671114802361</v>
+        <v>0.0331856943666935</v>
       </c>
       <c r="C14" s="1">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1883,16 +1802,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>0.03309066966176033</v>
+        <v>0.03104468062520027</v>
       </c>
       <c r="C15" s="1">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1909,16 +1828,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>0.03202322870492935</v>
+        <v>0.02676265500485897</v>
       </c>
       <c r="C16" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1935,16 +1854,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>0.03095578588545322</v>
+        <v>0.0251568965613842</v>
       </c>
       <c r="C17" s="1">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1961,16 +1880,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>0.02775346301496029</v>
+        <v>0.0251568965613842</v>
       </c>
       <c r="C18" s="1">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1987,16 +1906,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>0.02668602205812931</v>
+        <v>0.02141012437641621</v>
       </c>
       <c r="C19" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2013,16 +1932,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>0.02508486062288284</v>
+        <v>0.0208748709410429</v>
       </c>
       <c r="C20" s="1">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2039,16 +1958,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>0.02508486062288284</v>
+        <v>0.0208748709410429</v>
       </c>
       <c r="C21" s="1">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2065,16 +1984,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>0.02134881913661957</v>
+        <v>0.02033961750566959</v>
       </c>
       <c r="C22" s="1">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2091,16 +2010,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>0.02081509865820408</v>
+        <v>0.01980436407029629</v>
       </c>
       <c r="C23" s="1">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2117,16 +2036,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.02081509865820408</v>
+        <v>0.01926911249756813</v>
       </c>
       <c r="C24" s="1">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2143,16 +2062,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02028137817978859</v>
+        <v>0.01873385906219482</v>
       </c>
       <c r="C25" s="1">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2169,16 +2088,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>0.0197476577013731</v>
+        <v>0.01819860562682152</v>
       </c>
       <c r="C26" s="1">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2195,16 +2114,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.01921393722295761</v>
+        <v>0.01766335219144821</v>
       </c>
       <c r="C27" s="1">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2221,16 +2140,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>0.01868021674454212</v>
+        <v>0.01659284718334675</v>
       </c>
       <c r="C28" s="1">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2247,16 +2166,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>0.01814649626612663</v>
+        <v>0.01391658093780279</v>
       </c>
       <c r="C29" s="1">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2273,16 +2192,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>0.01761277578771114</v>
+        <v>0.01391658093780279</v>
       </c>
       <c r="C30" s="1">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2299,16 +2218,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>0.01654533483088017</v>
+        <v>0.01338132750242949</v>
       </c>
       <c r="C31" s="1">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2325,16 +2244,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>0.01387673150748015</v>
+        <v>0.01177556812763214</v>
       </c>
       <c r="C32" s="1">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2351,16 +2270,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>0.01387673150748015</v>
+        <v>0.01177556812763214</v>
       </c>
       <c r="C33" s="1">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2377,16 +2296,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01334301102906466</v>
+        <v>0.008564049378037453</v>
       </c>
       <c r="C34" s="1">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2403,16 +2322,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="2">
-        <v>0.01280929055064917</v>
+        <v>0.007493543438613415</v>
       </c>
       <c r="C35" s="1">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2429,16 +2348,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="2">
-        <v>0.01174185052514076</v>
+        <v>0.007493543438613415</v>
       </c>
       <c r="C36" s="1">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2455,16 +2374,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>0.01174185052514076</v>
+        <v>0.006958290468901396</v>
       </c>
       <c r="C37" s="1">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2481,16 +2400,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>0.009606968611478806</v>
+        <v>0.006958290468901396</v>
       </c>
       <c r="C38" s="1">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2507,16 +2426,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.008539527654647827</v>
+        <v>0.006958290468901396</v>
       </c>
       <c r="C39" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -2533,16 +2452,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.007472086232155561</v>
+        <v>0.005887784063816071</v>
       </c>
       <c r="C40" s="1">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -2559,16 +2478,16 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.007472086232155561</v>
+        <v>0.004817278124392033</v>
       </c>
       <c r="C41" s="1">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -2585,16 +2504,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.006938365753740072</v>
+        <v>0.004282024689018726</v>
       </c>
       <c r="C42" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -2611,16 +2530,16 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.006938365753740072</v>
+        <v>0.004282024689018726</v>
       </c>
       <c r="C43" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -2637,16 +2556,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.006938365753740072</v>
+        <v>0.003746771719306707</v>
       </c>
       <c r="C44" s="1">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -2663,16 +2582,16 @@
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.006404645275324583</v>
+        <v>0.003746771719306707</v>
       </c>
       <c r="C45" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -2689,16 +2608,16 @@
         <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.005870925262570381</v>
+        <v>0.003746771719306707</v>
       </c>
       <c r="C46" s="1">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -2715,16 +2634,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.004803484305739403</v>
+        <v>0.003211518749594688</v>
       </c>
       <c r="C47" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -2738,45 +2657,45 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>0.004269763827323914</v>
+        <v>0.003211518749594688</v>
       </c>
       <c r="C48" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="E48" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>0.004269763827323914</v>
+        <v>0.003211518749594688</v>
       </c>
       <c r="C49" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -2790,19 +2709,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>0.003736043116077781</v>
+        <v>0.003211518749594688</v>
       </c>
       <c r="C50" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -2816,19 +2735,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>0.003736043116077781</v>
+        <v>0.002676265547052026</v>
       </c>
       <c r="C51" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -2842,19 +2761,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="2">
-        <v>0.003736043116077781</v>
+        <v>0.002676265547052026</v>
       </c>
       <c r="C52" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -2868,19 +2787,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>0.003202322637662292</v>
+        <v>0.002141012344509363</v>
       </c>
       <c r="C53" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -2894,45 +2813,45 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B54" s="2">
-        <v>0.003202322637662292</v>
+        <v>0.002141012344509363</v>
       </c>
       <c r="C54" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D54" s="1">
-        <v>264</v>
+        <v>96</v>
       </c>
       <c r="E54" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>252</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.003202322637662292</v>
+        <v>0.002141012344509363</v>
       </c>
       <c r="C55" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -2946,19 +2865,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.003202322637662292</v>
+        <v>0.001605759374797344</v>
       </c>
       <c r="C56" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -2972,19 +2891,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>0.002668602392077446</v>
+        <v>0.001605759374797344</v>
       </c>
       <c r="C57" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -2998,19 +2917,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>0.002668602392077446</v>
+        <v>0.001605759374797344</v>
       </c>
       <c r="C58" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3024,19 +2943,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.002134881913661957</v>
+        <v>0.001070506172254682</v>
       </c>
       <c r="C59" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3050,19 +2969,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.002134881913661957</v>
+        <v>0.0005352530861273408</v>
       </c>
       <c r="C60" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D60" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3071,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -3079,16 +2998,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.002134881913661957</v>
+        <v>0.0005352530861273408</v>
       </c>
       <c r="C61" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3105,16 +3024,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.002134881913661957</v>
+        <v>0.0005352530861273408</v>
       </c>
       <c r="C62" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3131,16 +3050,16 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.001601161318831146</v>
+        <v>0.0005352530861273408</v>
       </c>
       <c r="C63" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3153,268 +3072,34 @@
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B64" s="2">
-        <v>0.001601161318831146</v>
-      </c>
-      <c r="C64" s="1">
-        <v>6</v>
-      </c>
-      <c r="D64" s="1">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1">
-        <v>6</v>
-      </c>
-      <c r="F64" s="1">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0</v>
-      </c>
-      <c r="H64" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="1" t="s">
+      <c r="A64" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="2">
-        <v>0.001601161318831146</v>
-      </c>
-      <c r="C65" s="1">
-        <v>6</v>
-      </c>
-      <c r="D65" s="1">
-        <v>0</v>
-      </c>
-      <c r="E65" s="1">
-        <v>6</v>
-      </c>
-      <c r="F65" s="1">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0</v>
-      </c>
-      <c r="H65" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" s="2">
-        <v>0.001601161318831146</v>
-      </c>
-      <c r="C66" s="1">
-        <v>6</v>
-      </c>
-      <c r="D66" s="1">
-        <v>0</v>
-      </c>
-      <c r="E66" s="1">
-        <v>6</v>
-      </c>
-      <c r="F66" s="1">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="2">
-        <v>0.001067440956830978</v>
-      </c>
-      <c r="C67" s="1">
-        <v>4</v>
-      </c>
-      <c r="D67" s="1">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1">
-        <v>4</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0</v>
-      </c>
-      <c r="H67" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B68" s="2">
-        <v>0.001067440956830978</v>
-      </c>
-      <c r="C68" s="1">
-        <v>4</v>
-      </c>
-      <c r="D68" s="1">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1">
-        <v>4</v>
-      </c>
-      <c r="F68" s="1">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69" s="2">
-        <v>0.0005337204784154892</v>
-      </c>
-      <c r="C69" s="1">
-        <v>2</v>
-      </c>
-      <c r="D69" s="1">
-        <v>0</v>
-      </c>
-      <c r="E69" s="1">
-        <v>2</v>
-      </c>
-      <c r="F69" s="1">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0</v>
-      </c>
-      <c r="H69" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B70" s="2">
-        <v>0.0005337204784154892</v>
-      </c>
-      <c r="C70" s="1">
-        <v>2</v>
-      </c>
-      <c r="D70" s="1">
-        <v>0</v>
-      </c>
-      <c r="E70" s="1">
-        <v>2</v>
-      </c>
-      <c r="F70" s="1">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0</v>
-      </c>
-      <c r="H70" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71" s="2">
-        <v>0.0005337204784154892</v>
-      </c>
-      <c r="C71" s="1">
-        <v>2</v>
-      </c>
-      <c r="D71" s="1">
-        <v>0</v>
-      </c>
-      <c r="E71" s="1">
-        <v>2</v>
-      </c>
-      <c r="F71" s="1">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0</v>
-      </c>
-      <c r="H71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="2">
-        <v>0.0005337204784154892</v>
-      </c>
-      <c r="C72" s="1">
-        <v>2</v>
-      </c>
-      <c r="D72" s="1">
-        <v>0</v>
-      </c>
-      <c r="E72" s="1">
-        <v>2</v>
-      </c>
-      <c r="F72" s="1">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0</v>
-      </c>
-      <c r="H72" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" t="s">
-        <v>72</v>
-      </c>
-      <c r="B73">
+      <c r="B64">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C73">
+      <c r="C64">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D73">
+      <c r="D64">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E73">
+      <c r="E64">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F73">
+      <c r="F64">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G73">
+      <c r="G64">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H73">
+      <c r="H64">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
